--- a/research/traditional_assets/database/data/croatia/croatia_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_healthcare_support_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09467086218488645</v>
+        <v>0.09453735463295365</v>
       </c>
       <c r="C2">
-        <v>236.3531576820113</v>
+        <v>234.4181768032078</v>
       </c>
       <c r="D2">
-        <v>232.7131576820113</v>
+        <v>233.1191768032079</v>
       </c>
       <c r="E2">
-        <v>-69.2</v>
+        <v>-66.85900000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.341</v>
       </c>
       <c r="G2">
         <v>3.64</v>
@@ -1451,28 +1451,28 @@
         <v>22.79</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1177523</v>
       </c>
       <c r="N2">
-        <v>22.79</v>
+        <v>22.6722477</v>
       </c>
       <c r="O2">
-        <v>4.1022</v>
+        <v>4.081004586</v>
       </c>
       <c r="P2">
-        <v>18.6878</v>
+        <v>18.591243114</v>
       </c>
       <c r="Q2">
-        <v>23.8978</v>
+        <v>23.801243114</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09467086218488645</v>
+        <v>0.09507565114439763</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738456</v>
+        <v>0.8308582687597704</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>193.5418671227653</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09453735463295365</v>
+        <v>0.09440384708102087</v>
       </c>
       <c r="C3">
-        <v>234.4181768032078</v>
+        <v>232.4846151793424</v>
       </c>
       <c r="D3">
-        <v>233.1191768032079</v>
+        <v>233.5266151793424</v>
       </c>
       <c r="E3">
-        <v>-66.85900000000001</v>
+        <v>-64.518</v>
       </c>
       <c r="F3">
-        <v>2.341</v>
+        <v>4.682</v>
       </c>
       <c r="G3">
         <v>3.64</v>
@@ -1533,28 +1533,28 @@
         <v>22.79</v>
       </c>
       <c r="M3">
-        <v>0.1177523</v>
+        <v>0.2355046</v>
       </c>
       <c r="N3">
-        <v>22.6722477</v>
+        <v>22.5544954</v>
       </c>
       <c r="O3">
-        <v>4.081004586</v>
+        <v>4.059809172</v>
       </c>
       <c r="P3">
-        <v>18.591243114</v>
+        <v>18.494686228</v>
       </c>
       <c r="Q3">
-        <v>23.801243114</v>
+        <v>23.704686228</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09507565114439763</v>
+        <v>0.09548870110308251</v>
       </c>
       <c r="T3">
-        <v>0.8308582687597704</v>
+        <v>0.8378228844596937</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>193.5418671227653</v>
+        <v>96.77093356138266</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09440384708102087</v>
+        <v>0.09427033952908807</v>
       </c>
       <c r="C4">
-        <v>232.4846151793424</v>
+        <v>230.5524802650317</v>
       </c>
       <c r="D4">
-        <v>233.5266151793424</v>
+        <v>233.9354802650317</v>
       </c>
       <c r="E4">
-        <v>-64.518</v>
+        <v>-62.177</v>
       </c>
       <c r="F4">
-        <v>4.682</v>
+        <v>7.023000000000001</v>
       </c>
       <c r="G4">
         <v>3.64</v>
@@ -1615,28 +1615,28 @@
         <v>22.79</v>
       </c>
       <c r="M4">
-        <v>0.2355046</v>
+        <v>0.3532569</v>
       </c>
       <c r="N4">
-        <v>22.5544954</v>
+        <v>22.4367431</v>
       </c>
       <c r="O4">
-        <v>4.059809172</v>
+        <v>4.038613757999999</v>
       </c>
       <c r="P4">
-        <v>18.494686228</v>
+        <v>18.398129342</v>
       </c>
       <c r="Q4">
-        <v>23.704686228</v>
+        <v>23.608129342</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09548870110308251</v>
+        <v>0.0959102675557609</v>
       </c>
       <c r="T4">
-        <v>0.8378228844596937</v>
+        <v>0.8449311004833268</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.77093356138266</v>
+        <v>64.51395570758844</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09427033952908807</v>
+        <v>0.09413683197715526</v>
       </c>
       <c r="C5">
-        <v>230.5524802650317</v>
+        <v>228.6217795671907</v>
       </c>
       <c r="D5">
-        <v>233.9354802650317</v>
+        <v>234.3457795671908</v>
       </c>
       <c r="E5">
-        <v>-62.177</v>
+        <v>-59.836</v>
       </c>
       <c r="F5">
-        <v>7.023000000000001</v>
+        <v>9.364000000000001</v>
       </c>
       <c r="G5">
         <v>3.64</v>
@@ -1697,28 +1697,28 @@
         <v>22.79</v>
       </c>
       <c r="M5">
-        <v>0.3532569</v>
+        <v>0.4710092</v>
       </c>
       <c r="N5">
-        <v>22.4367431</v>
+        <v>22.3189908</v>
       </c>
       <c r="O5">
-        <v>4.038613757999999</v>
+        <v>4.017418343999999</v>
       </c>
       <c r="P5">
-        <v>18.398129342</v>
+        <v>18.301572456</v>
       </c>
       <c r="Q5">
-        <v>23.608129342</v>
+        <v>23.511572456</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0959102675557609</v>
+        <v>0.09634061664287007</v>
       </c>
       <c r="T5">
-        <v>0.8449311004833268</v>
+        <v>0.8521874043407853</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.51395570758844</v>
+        <v>48.38546678069132</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09413683197715526</v>
+        <v>0.09400332442522247</v>
       </c>
       <c r="C6">
-        <v>228.6217795671907</v>
+        <v>226.6925206454928</v>
       </c>
       <c r="D6">
-        <v>234.3457795671908</v>
+        <v>234.7575206454929</v>
       </c>
       <c r="E6">
-        <v>-59.836</v>
+        <v>-57.495</v>
       </c>
       <c r="F6">
-        <v>9.364000000000001</v>
+        <v>11.705</v>
       </c>
       <c r="G6">
         <v>3.64</v>
@@ -1779,28 +1779,28 @@
         <v>22.79</v>
       </c>
       <c r="M6">
-        <v>0.4710092</v>
+        <v>0.5887615</v>
       </c>
       <c r="N6">
-        <v>22.3189908</v>
+        <v>22.2012385</v>
       </c>
       <c r="O6">
-        <v>4.017418343999999</v>
+        <v>3.99622293</v>
       </c>
       <c r="P6">
-        <v>18.301572456</v>
+        <v>18.20501557</v>
       </c>
       <c r="Q6">
-        <v>23.511572456</v>
+        <v>23.41501557</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09634061664287007</v>
+        <v>0.0967800257107605</v>
       </c>
       <c r="T6">
-        <v>0.8521874043407853</v>
+        <v>0.8595964724899799</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.38546678069132</v>
+        <v>38.70837342455306</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09400332442522247</v>
+        <v>0.09386981687328967</v>
       </c>
       <c r="C7">
-        <v>226.6925206454928</v>
+        <v>224.7647111128334</v>
       </c>
       <c r="D7">
-        <v>234.7575206454929</v>
+        <v>235.1707111128334</v>
       </c>
       <c r="E7">
-        <v>-57.495</v>
+        <v>-55.154</v>
       </c>
       <c r="F7">
-        <v>11.705</v>
+        <v>14.046</v>
       </c>
       <c r="G7">
         <v>3.64</v>
@@ -1861,28 +1861,28 @@
         <v>22.79</v>
       </c>
       <c r="M7">
-        <v>0.5887615</v>
+        <v>0.7065138000000001</v>
       </c>
       <c r="N7">
-        <v>22.2012385</v>
+        <v>22.0834862</v>
       </c>
       <c r="O7">
-        <v>3.99622293</v>
+        <v>3.975027516</v>
       </c>
       <c r="P7">
-        <v>18.20501557</v>
+        <v>18.108458684</v>
       </c>
       <c r="Q7">
-        <v>23.41501557</v>
+        <v>23.318458684</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0967800257107605</v>
+        <v>0.09722878390775497</v>
       </c>
       <c r="T7">
-        <v>0.8595964724899799</v>
+        <v>0.8671631803870299</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.70837342455306</v>
+        <v>32.25697785379422</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09386981687328967</v>
+        <v>0.09373630932135688</v>
       </c>
       <c r="C8">
-        <v>224.7647111128334</v>
+        <v>222.8383586357996</v>
       </c>
       <c r="D8">
-        <v>235.1707111128334</v>
+        <v>235.5853586357996</v>
       </c>
       <c r="E8">
-        <v>-55.154</v>
+        <v>-52.813</v>
       </c>
       <c r="F8">
-        <v>14.046</v>
+        <v>16.387</v>
       </c>
       <c r="G8">
         <v>3.64</v>
@@ -1943,28 +1943,28 @@
         <v>22.79</v>
       </c>
       <c r="M8">
-        <v>0.7065138</v>
+        <v>0.8242661</v>
       </c>
       <c r="N8">
-        <v>22.0834862</v>
+        <v>21.9657339</v>
       </c>
       <c r="O8">
-        <v>3.975027516</v>
+        <v>3.953832102</v>
       </c>
       <c r="P8">
-        <v>18.108458684</v>
+        <v>18.011901798</v>
       </c>
       <c r="Q8">
-        <v>23.318458684</v>
+        <v>23.221901798</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09722878390775497</v>
+        <v>0.09768719281866331</v>
       </c>
       <c r="T8">
-        <v>0.8671631803870299</v>
+        <v>0.8748926131850916</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.25697785379423</v>
+        <v>27.64883816039505</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09373630932135686</v>
+        <v>0.09360280176942409</v>
       </c>
       <c r="C9">
-        <v>222.8383586357996</v>
+        <v>220.9134709351439</v>
       </c>
       <c r="D9">
-        <v>235.5853586357997</v>
+        <v>236.001470935144</v>
       </c>
       <c r="E9">
-        <v>-52.813</v>
+        <v>-50.472</v>
       </c>
       <c r="F9">
-        <v>16.387</v>
+        <v>18.728</v>
       </c>
       <c r="G9">
         <v>3.64</v>
@@ -2025,28 +2025,28 @@
         <v>22.79</v>
       </c>
       <c r="M9">
-        <v>0.8242661000000001</v>
+        <v>0.9420184</v>
       </c>
       <c r="N9">
-        <v>21.9657339</v>
+        <v>21.8479816</v>
       </c>
       <c r="O9">
-        <v>3.953832102</v>
+        <v>3.932636688</v>
       </c>
       <c r="P9">
-        <v>18.011901798</v>
+        <v>17.915344912</v>
       </c>
       <c r="Q9">
-        <v>23.221901798</v>
+        <v>23.125344912</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09768719281866331</v>
+        <v>0.09815556714067836</v>
       </c>
       <c r="T9">
-        <v>0.8748926131850916</v>
+        <v>0.8827900771309374</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.64883816039504</v>
+        <v>24.19273339034567</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09360280176942409</v>
+        <v>0.0934692942174913</v>
       </c>
       <c r="C10">
-        <v>220.9134709351439</v>
+        <v>218.9900557862643</v>
       </c>
       <c r="D10">
-        <v>236.001470935144</v>
+        <v>236.4190557862644</v>
       </c>
       <c r="E10">
-        <v>-50.472</v>
+        <v>-48.131</v>
       </c>
       <c r="F10">
-        <v>18.728</v>
+        <v>21.069</v>
       </c>
       <c r="G10">
         <v>3.64</v>
@@ -2107,28 +2107,28 @@
         <v>22.79</v>
       </c>
       <c r="M10">
-        <v>0.9420184</v>
+        <v>1.0597707</v>
       </c>
       <c r="N10">
-        <v>21.8479816</v>
+        <v>21.7302293</v>
       </c>
       <c r="O10">
-        <v>3.932636688</v>
+        <v>3.911441274</v>
       </c>
       <c r="P10">
-        <v>17.915344912</v>
+        <v>17.818788026</v>
       </c>
       <c r="Q10">
-        <v>23.125344912</v>
+        <v>23.028788026</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09815556714067836</v>
+        <v>0.09863423540383659</v>
       </c>
       <c r="T10">
-        <v>0.8827900771309374</v>
+        <v>0.8908611117129553</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.19273339034567</v>
+        <v>21.50465190252948</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0934692942174913</v>
+        <v>0.0933357866655585</v>
       </c>
       <c r="C11">
-        <v>218.9900557862643</v>
+        <v>217.0681210196874</v>
       </c>
       <c r="D11">
-        <v>236.4190557862644</v>
+        <v>236.8381210196874</v>
       </c>
       <c r="E11">
-        <v>-48.131</v>
+        <v>-45.79000000000001</v>
       </c>
       <c r="F11">
-        <v>21.069</v>
+        <v>23.41</v>
       </c>
       <c r="G11">
         <v>3.64</v>
@@ -2189,28 +2189,28 @@
         <v>22.79</v>
       </c>
       <c r="M11">
-        <v>1.0597707</v>
+        <v>1.177523</v>
       </c>
       <c r="N11">
-        <v>21.7302293</v>
+        <v>21.612477</v>
       </c>
       <c r="O11">
-        <v>3.911441274</v>
+        <v>3.890245859999999</v>
       </c>
       <c r="P11">
-        <v>17.818788026</v>
+        <v>17.72223114</v>
       </c>
       <c r="Q11">
-        <v>23.028788026</v>
+        <v>22.93223114</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09863423540383659</v>
+        <v>0.09912354073950944</v>
       </c>
       <c r="T11">
-        <v>0.8908611117129553</v>
+        <v>0.8991115026190183</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.50465190252948</v>
+        <v>19.35418671227653</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0933357866655585</v>
+        <v>0.09320227911362569</v>
       </c>
       <c r="C12">
-        <v>217.0681210196874</v>
+        <v>215.1476745215587</v>
       </c>
       <c r="D12">
-        <v>236.8381210196874</v>
+        <v>237.2586745215588</v>
       </c>
       <c r="E12">
-        <v>-45.79</v>
+        <v>-43.449</v>
       </c>
       <c r="F12">
-        <v>23.41</v>
+        <v>25.751</v>
       </c>
       <c r="G12">
         <v>3.64</v>
@@ -2271,28 +2271,28 @@
         <v>22.79</v>
       </c>
       <c r="M12">
-        <v>1.177523</v>
+        <v>1.2952753</v>
       </c>
       <c r="N12">
-        <v>21.612477</v>
+        <v>21.4947247</v>
       </c>
       <c r="O12">
-        <v>3.890245859999999</v>
+        <v>3.869050446</v>
       </c>
       <c r="P12">
-        <v>17.72223114</v>
+        <v>17.625674254</v>
       </c>
       <c r="Q12">
-        <v>22.93223114</v>
+        <v>22.835674254</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09912354073950944</v>
+        <v>0.09962384170070303</v>
       </c>
       <c r="T12">
-        <v>0.8991115026190183</v>
+        <v>0.907547295567914</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.35418671227653</v>
+        <v>17.59471519297867</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09320227911362569</v>
+        <v>0.09306877156169291</v>
       </c>
       <c r="C13">
-        <v>215.1476745215587</v>
+        <v>213.2287242341372</v>
       </c>
       <c r="D13">
-        <v>237.2586745215588</v>
+        <v>237.6807242341372</v>
       </c>
       <c r="E13">
-        <v>-43.449</v>
+        <v>-41.108</v>
       </c>
       <c r="F13">
-        <v>25.751</v>
+        <v>28.092</v>
       </c>
       <c r="G13">
         <v>3.64</v>
@@ -2353,28 +2353,28 @@
         <v>22.79</v>
       </c>
       <c r="M13">
-        <v>1.2952753</v>
+        <v>1.4130276</v>
       </c>
       <c r="N13">
-        <v>21.4947247</v>
+        <v>21.3769724</v>
       </c>
       <c r="O13">
-        <v>3.869050446</v>
+        <v>3.847855032</v>
       </c>
       <c r="P13">
-        <v>17.625674254</v>
+        <v>17.529117368</v>
       </c>
       <c r="Q13">
-        <v>22.835674254</v>
+        <v>22.739117368</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09962384170070303</v>
+        <v>0.1001355131382874</v>
       </c>
       <c r="T13">
-        <v>0.907547295567914</v>
+        <v>0.9161748110838301</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.59471519297867</v>
+        <v>16.12848892689711</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09306877156169291</v>
+        <v>0.09293526400976011</v>
       </c>
       <c r="C14">
-        <v>213.2287242341372</v>
+        <v>211.3112781562949</v>
       </c>
       <c r="D14">
-        <v>237.6807242341372</v>
+        <v>238.104278156295</v>
       </c>
       <c r="E14">
-        <v>-41.108</v>
+        <v>-38.767</v>
       </c>
       <c r="F14">
-        <v>28.092</v>
+        <v>30.433</v>
       </c>
       <c r="G14">
         <v>3.64</v>
@@ -2435,28 +2435,28 @@
         <v>22.79</v>
       </c>
       <c r="M14">
-        <v>1.4130276</v>
+        <v>1.5307799</v>
       </c>
       <c r="N14">
-        <v>21.3769724</v>
+        <v>21.2592201</v>
       </c>
       <c r="O14">
-        <v>3.847855032</v>
+        <v>3.826659618</v>
       </c>
       <c r="P14">
-        <v>17.529117368</v>
+        <v>17.432560482</v>
       </c>
       <c r="Q14">
-        <v>22.739117368</v>
+        <v>22.642560482</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1001355131382874</v>
+        <v>0.1006589471376553</v>
       </c>
       <c r="T14">
-        <v>0.9161748110838301</v>
+        <v>0.9250006602897675</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.12848892689711</v>
+        <v>14.88783593252041</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09293526400976011</v>
+        <v>0.09280175645782732</v>
       </c>
       <c r="C15">
-        <v>211.3112781562949</v>
+        <v>209.395344344023</v>
       </c>
       <c r="D15">
-        <v>238.104278156295</v>
+        <v>238.529344344023</v>
       </c>
       <c r="E15">
-        <v>-38.767</v>
+        <v>-36.42599999999999</v>
       </c>
       <c r="F15">
-        <v>30.433</v>
+        <v>32.77400000000001</v>
       </c>
       <c r="G15">
         <v>3.64</v>
@@ -2517,28 +2517,28 @@
         <v>22.79</v>
       </c>
       <c r="M15">
-        <v>1.5307799</v>
+        <v>1.6485322</v>
       </c>
       <c r="N15">
-        <v>21.2592201</v>
+        <v>21.1414678</v>
       </c>
       <c r="O15">
-        <v>3.826659618</v>
+        <v>3.805464203999999</v>
       </c>
       <c r="P15">
-        <v>17.432560482</v>
+        <v>17.336003596</v>
       </c>
       <c r="Q15">
-        <v>22.642560482</v>
+        <v>22.546003596</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1006589471376553</v>
+        <v>0.1011945540207294</v>
       </c>
       <c r="T15">
-        <v>0.9250006602897675</v>
+        <v>0.9340317618028195</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.88783593252041</v>
+        <v>13.82441908019752</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09280175645782732</v>
+        <v>0.09266824890589451</v>
       </c>
       <c r="C16">
-        <v>209.395344344023</v>
+        <v>207.4809309109415</v>
       </c>
       <c r="D16">
-        <v>238.529344344023</v>
+        <v>238.9559309109416</v>
       </c>
       <c r="E16">
-        <v>-36.42599999999999</v>
+        <v>-34.08499999999999</v>
       </c>
       <c r="F16">
-        <v>32.77400000000001</v>
+        <v>35.11500000000001</v>
       </c>
       <c r="G16">
         <v>3.64</v>
@@ -2599,28 +2599,28 @@
         <v>22.79</v>
       </c>
       <c r="M16">
-        <v>1.6485322</v>
+        <v>1.7662845</v>
       </c>
       <c r="N16">
-        <v>21.1414678</v>
+        <v>21.0237155</v>
       </c>
       <c r="O16">
-        <v>3.805464203999999</v>
+        <v>3.78426879</v>
       </c>
       <c r="P16">
-        <v>17.336003596</v>
+        <v>17.23944671</v>
       </c>
       <c r="Q16">
-        <v>22.546003596</v>
+        <v>22.44944671</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1011945540207294</v>
+        <v>0.1017427634186994</v>
       </c>
       <c r="T16">
-        <v>0.9340317618028195</v>
+        <v>0.943275359822061</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.82441908019752</v>
+        <v>12.90279114151768</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09266824890589451</v>
+        <v>0.09273154135396172</v>
       </c>
       <c r="C17">
-        <v>207.4809309109415</v>
+        <v>204.9375072930785</v>
       </c>
       <c r="D17">
-        <v>238.9559309109416</v>
+        <v>238.7535072930785</v>
       </c>
       <c r="E17">
-        <v>-34.085</v>
+        <v>-31.744</v>
       </c>
       <c r="F17">
-        <v>35.115</v>
+        <v>37.456</v>
       </c>
       <c r="G17">
         <v>3.64</v>
@@ -2681,45 +2681,45 @@
         <v>22.79</v>
       </c>
       <c r="M17">
-        <v>1.7662845</v>
+        <v>1.9402208</v>
       </c>
       <c r="N17">
-        <v>21.0237155</v>
+        <v>20.8497792</v>
       </c>
       <c r="O17">
-        <v>3.78426879</v>
+        <v>3.752960256</v>
       </c>
       <c r="P17">
-        <v>17.23944671</v>
+        <v>17.096818944</v>
       </c>
       <c r="Q17">
-        <v>22.44944671</v>
+        <v>22.306818944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1017427634186994</v>
+        <v>0.102304025421383</v>
       </c>
       <c r="T17">
-        <v>0.943275359822061</v>
+        <v>0.9527390435084273</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.18</v>
       </c>
       <c r="W17">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>12.90279114151769</v>
+        <v>11.74608580631648</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09273154135396172</v>
+        <v>0.09261033380202892</v>
       </c>
       <c r="C18">
-        <v>204.9375072930785</v>
+        <v>202.9844575341592</v>
       </c>
       <c r="D18">
-        <v>238.7535072930785</v>
+        <v>239.1414575341593</v>
       </c>
       <c r="E18">
-        <v>-31.744</v>
+        <v>-29.403</v>
       </c>
       <c r="F18">
-        <v>37.456</v>
+        <v>39.797</v>
       </c>
       <c r="G18">
         <v>3.64</v>
@@ -2763,28 +2763,28 @@
         <v>22.79</v>
       </c>
       <c r="M18">
-        <v>1.9402208</v>
+        <v>2.0614846</v>
       </c>
       <c r="N18">
-        <v>20.8497792</v>
+        <v>20.7285154</v>
       </c>
       <c r="O18">
-        <v>3.752960256</v>
+        <v>3.731132772</v>
       </c>
       <c r="P18">
-        <v>17.096818944</v>
+        <v>16.997382628</v>
       </c>
       <c r="Q18">
-        <v>22.306818944</v>
+        <v>22.207382628</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.102304025421383</v>
+        <v>0.1028788118096734</v>
       </c>
       <c r="T18">
-        <v>0.9527390435084273</v>
+        <v>0.9624307677655494</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.74608580631648</v>
+        <v>11.05513958241551</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09261033380202892</v>
+        <v>0.09248912625009613</v>
       </c>
       <c r="C19">
-        <v>202.9844575341592</v>
+        <v>201.0326705867922</v>
       </c>
       <c r="D19">
-        <v>239.1414575341593</v>
+        <v>239.5306705867923</v>
       </c>
       <c r="E19">
-        <v>-29.403</v>
+        <v>-27.06199999999999</v>
       </c>
       <c r="F19">
-        <v>39.797</v>
+        <v>42.13800000000001</v>
       </c>
       <c r="G19">
         <v>3.64</v>
@@ -2845,28 +2845,28 @@
         <v>22.79</v>
       </c>
       <c r="M19">
-        <v>2.0614846</v>
+        <v>2.182748400000001</v>
       </c>
       <c r="N19">
-        <v>20.7285154</v>
+        <v>20.6072516</v>
       </c>
       <c r="O19">
-        <v>3.731132772</v>
+        <v>3.709305287999999</v>
       </c>
       <c r="P19">
-        <v>16.997382628</v>
+        <v>16.897946312</v>
       </c>
       <c r="Q19">
-        <v>22.207382628</v>
+        <v>22.107946312</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1028788118096734</v>
+        <v>0.103467617378166</v>
       </c>
       <c r="T19">
-        <v>0.9624307677655494</v>
+        <v>0.972358875541138</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.05513958241551</v>
+        <v>10.4409651611702</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09248912625009614</v>
+        <v>0.09236791869816334</v>
       </c>
       <c r="C20">
-        <v>201.0326705867922</v>
+        <v>199.0821526268701</v>
       </c>
       <c r="D20">
-        <v>239.5306705867922</v>
+        <v>239.9211526268702</v>
       </c>
       <c r="E20">
-        <v>-27.062</v>
+        <v>-24.721</v>
       </c>
       <c r="F20">
-        <v>42.13800000000001</v>
+        <v>44.47900000000001</v>
       </c>
       <c r="G20">
         <v>3.64</v>
@@ -2927,28 +2927,28 @@
         <v>22.79</v>
       </c>
       <c r="M20">
-        <v>2.1827484</v>
+        <v>2.3040122</v>
       </c>
       <c r="N20">
-        <v>20.6072516</v>
+        <v>20.4859878</v>
       </c>
       <c r="O20">
-        <v>3.709305287999999</v>
+        <v>3.687477804</v>
       </c>
       <c r="P20">
-        <v>16.897946312</v>
+        <v>16.798509996</v>
       </c>
       <c r="Q20">
-        <v>22.107946312</v>
+        <v>22.008509996</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.103467617378166</v>
+        <v>0.1040709613557572</v>
       </c>
       <c r="T20">
-        <v>0.9723588755411378</v>
+        <v>0.9825321217803211</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.4409651611702</v>
+        <v>9.891440679003347</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09236791869816334</v>
+        <v>0.09252551114623055</v>
       </c>
       <c r="C21">
-        <v>199.0821526268701</v>
+        <v>196.2337009922532</v>
       </c>
       <c r="D21">
-        <v>239.9211526268702</v>
+        <v>239.4137009922532</v>
       </c>
       <c r="E21">
-        <v>-24.721</v>
+        <v>-22.38</v>
       </c>
       <c r="F21">
-        <v>44.47900000000001</v>
+        <v>46.82000000000001</v>
       </c>
       <c r="G21">
         <v>3.64</v>
@@ -3009,45 +3009,45 @@
         <v>22.79</v>
       </c>
       <c r="M21">
-        <v>2.3040122</v>
+        <v>2.50487</v>
       </c>
       <c r="N21">
-        <v>20.4859878</v>
+        <v>20.28513</v>
       </c>
       <c r="O21">
-        <v>3.687477804</v>
+        <v>3.651323399999999</v>
       </c>
       <c r="P21">
-        <v>16.798509996</v>
+        <v>16.6338066</v>
       </c>
       <c r="Q21">
-        <v>22.008509996</v>
+        <v>21.8438066</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1040709613557572</v>
+        <v>0.1046893889327882</v>
       </c>
       <c r="T21">
-        <v>0.9825321217803211</v>
+        <v>0.9929596991754841</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.18</v>
       </c>
       <c r="W21">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.891440679003347</v>
+        <v>9.098276557266443</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09252551114623055</v>
+        <v>0.09241824359429775</v>
       </c>
       <c r="C22">
-        <v>196.2337009922532</v>
+        <v>194.2378715702672</v>
       </c>
       <c r="D22">
-        <v>239.4137009922532</v>
+        <v>239.7588715702672</v>
       </c>
       <c r="E22">
-        <v>-22.38</v>
+        <v>-20.03899999999999</v>
       </c>
       <c r="F22">
-        <v>46.82000000000001</v>
+        <v>49.16100000000001</v>
       </c>
       <c r="G22">
         <v>3.64</v>
@@ -3091,28 +3091,28 @@
         <v>22.79</v>
       </c>
       <c r="M22">
-        <v>2.50487</v>
+        <v>2.6301135</v>
       </c>
       <c r="N22">
-        <v>20.28513</v>
+        <v>20.1598865</v>
       </c>
       <c r="O22">
-        <v>3.651323399999999</v>
+        <v>3.62877957</v>
       </c>
       <c r="P22">
-        <v>16.6338066</v>
+        <v>16.53110693</v>
       </c>
       <c r="Q22">
-        <v>21.8438066</v>
+        <v>21.74110693</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1046893889327882</v>
+        <v>0.1053234729041743</v>
       </c>
       <c r="T22">
-        <v>0.9929596991754841</v>
+        <v>1.00365126587179</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.098276557266443</v>
+        <v>8.665025292634709</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09241824359429775</v>
+        <v>0.09231097604236495</v>
       </c>
       <c r="C23">
-        <v>194.2378715702672</v>
+        <v>192.2430388727579</v>
       </c>
       <c r="D23">
-        <v>239.7588715702672</v>
+        <v>240.1050388727579</v>
       </c>
       <c r="E23">
-        <v>-20.039</v>
+        <v>-17.698</v>
       </c>
       <c r="F23">
-        <v>49.161</v>
+        <v>51.502</v>
       </c>
       <c r="G23">
         <v>3.64</v>
@@ -3173,28 +3173,28 @@
         <v>22.79</v>
       </c>
       <c r="M23">
-        <v>2.6301135</v>
+        <v>2.755357</v>
       </c>
       <c r="N23">
-        <v>20.1598865</v>
+        <v>20.034643</v>
       </c>
       <c r="O23">
-        <v>3.62877957</v>
+        <v>3.60623574</v>
       </c>
       <c r="P23">
-        <v>16.53110693</v>
+        <v>16.42840726</v>
       </c>
       <c r="Q23">
-        <v>21.74110693</v>
+        <v>21.63840726</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1053234729041743</v>
+        <v>0.1059738154389294</v>
       </c>
       <c r="T23">
-        <v>1.00365126587179</v>
+        <v>1.014616975303899</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.665025292634709</v>
+        <v>8.27116050660586</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09231097604236495</v>
+        <v>0.09220370849043216</v>
       </c>
       <c r="C24">
-        <v>192.2430388727579</v>
+        <v>190.2492072232227</v>
       </c>
       <c r="D24">
-        <v>240.1050388727579</v>
+        <v>240.4522072232228</v>
       </c>
       <c r="E24">
-        <v>-17.698</v>
+        <v>-15.35699999999999</v>
       </c>
       <c r="F24">
-        <v>51.502</v>
+        <v>53.84300000000001</v>
       </c>
       <c r="G24">
         <v>3.64</v>
@@ -3255,28 +3255,28 @@
         <v>22.79</v>
       </c>
       <c r="M24">
-        <v>2.755357</v>
+        <v>2.8806005</v>
       </c>
       <c r="N24">
-        <v>20.034643</v>
+        <v>19.9093995</v>
       </c>
       <c r="O24">
-        <v>3.60623574</v>
+        <v>3.58369191</v>
       </c>
       <c r="P24">
-        <v>16.42840726</v>
+        <v>16.32570759</v>
       </c>
       <c r="Q24">
-        <v>21.63840726</v>
+        <v>21.53570759</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1059738154389294</v>
+        <v>0.1066410499875742</v>
       </c>
       <c r="T24">
-        <v>1.014616975303899</v>
+        <v>1.025867508357621</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.27116050660586</v>
+        <v>7.911544832405603</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09220370849043216</v>
+        <v>0.09225388093849936</v>
       </c>
       <c r="C25">
-        <v>190.2492072232227</v>
+        <v>187.7457006505846</v>
       </c>
       <c r="D25">
-        <v>240.4522072232228</v>
+        <v>240.2897006505846</v>
       </c>
       <c r="E25">
-        <v>-15.35699999999999</v>
+        <v>-13.01599999999999</v>
       </c>
       <c r="F25">
-        <v>53.84300000000001</v>
+        <v>56.18400000000001</v>
       </c>
       <c r="G25">
         <v>3.64</v>
@@ -3337,45 +3337,45 @@
         <v>22.79</v>
       </c>
       <c r="M25">
-        <v>2.8806005</v>
+        <v>3.050791200000001</v>
       </c>
       <c r="N25">
-        <v>19.9093995</v>
+        <v>19.7392088</v>
       </c>
       <c r="O25">
-        <v>3.58369191</v>
+        <v>3.553057584</v>
       </c>
       <c r="P25">
-        <v>16.32570759</v>
+        <v>16.186151216</v>
       </c>
       <c r="Q25">
-        <v>21.53570759</v>
+        <v>21.396151216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1066410499875742</v>
+        <v>0.1073258433401307</v>
       </c>
       <c r="T25">
-        <v>1.025867508357621</v>
+        <v>1.037414108070652</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.18</v>
       </c>
       <c r="W25">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.911544832405603</v>
+        <v>7.470193305920115</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09225388093849936</v>
+        <v>0.09215317338656656</v>
       </c>
       <c r="C26">
-        <v>187.7457006505846</v>
+        <v>185.7311107685756</v>
       </c>
       <c r="D26">
-        <v>240.2897006505846</v>
+        <v>240.6161107685757</v>
       </c>
       <c r="E26">
-        <v>-13.016</v>
+        <v>-10.675</v>
       </c>
       <c r="F26">
-        <v>56.184</v>
+        <v>58.52500000000001</v>
       </c>
       <c r="G26">
         <v>3.64</v>
@@ -3419,28 +3419,28 @@
         <v>22.79</v>
       </c>
       <c r="M26">
-        <v>3.0507912</v>
+        <v>3.1779075</v>
       </c>
       <c r="N26">
-        <v>19.7392088</v>
+        <v>19.6120925</v>
       </c>
       <c r="O26">
-        <v>3.553057584</v>
+        <v>3.53017665</v>
       </c>
       <c r="P26">
-        <v>16.186151216</v>
+        <v>16.08191585</v>
       </c>
       <c r="Q26">
-        <v>21.396151216</v>
+        <v>21.29191585</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1073258433401307</v>
+        <v>0.1080288978487554</v>
       </c>
       <c r="T26">
-        <v>1.037414108070652</v>
+        <v>1.049268617109363</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.470193305920116</v>
+        <v>7.171385573683311</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09215317338656656</v>
+        <v>0.09205246583463376</v>
       </c>
       <c r="C27">
-        <v>185.7311107685756</v>
+        <v>183.7174088854342</v>
       </c>
       <c r="D27">
-        <v>240.6161107685757</v>
+        <v>240.9434088854343</v>
       </c>
       <c r="E27">
-        <v>-10.675</v>
+        <v>-8.333999999999996</v>
       </c>
       <c r="F27">
-        <v>58.52500000000001</v>
+        <v>60.86600000000001</v>
       </c>
       <c r="G27">
         <v>3.64</v>
@@ -3501,28 +3501,28 @@
         <v>22.79</v>
       </c>
       <c r="M27">
-        <v>3.1779075</v>
+        <v>3.3050238</v>
       </c>
       <c r="N27">
-        <v>19.6120925</v>
+        <v>19.4849762</v>
       </c>
       <c r="O27">
-        <v>3.53017665</v>
+        <v>3.507295716</v>
       </c>
       <c r="P27">
-        <v>16.08191585</v>
+        <v>15.977680484</v>
       </c>
       <c r="Q27">
-        <v>21.29191585</v>
+        <v>21.187680484</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1080288978487554</v>
+        <v>0.1087509538305862</v>
       </c>
       <c r="T27">
-        <v>1.049268617109363</v>
+        <v>1.061443518284256</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.171385573683311</v>
+        <v>6.895563051618568</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09205246583463376</v>
+        <v>0.09195175828270097</v>
       </c>
       <c r="C28">
-        <v>183.7174088854342</v>
+        <v>181.7045986297982</v>
       </c>
       <c r="D28">
-        <v>240.9434088854343</v>
+        <v>241.2715986297982</v>
       </c>
       <c r="E28">
-        <v>-8.333999999999996</v>
+        <v>-5.992999999999995</v>
       </c>
       <c r="F28">
-        <v>60.86600000000001</v>
+        <v>63.20700000000001</v>
       </c>
       <c r="G28">
         <v>3.64</v>
@@ -3583,28 +3583,28 @@
         <v>22.79</v>
       </c>
       <c r="M28">
-        <v>3.3050238</v>
+        <v>3.432140100000001</v>
       </c>
       <c r="N28">
-        <v>19.4849762</v>
+        <v>19.3578599</v>
       </c>
       <c r="O28">
-        <v>3.507295716</v>
+        <v>3.484414782</v>
       </c>
       <c r="P28">
-        <v>15.977680484</v>
+        <v>15.873445118</v>
       </c>
       <c r="Q28">
-        <v>21.187680484</v>
+        <v>21.083445118</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1087509538305862</v>
+        <v>0.1094927921680835</v>
       </c>
       <c r="T28">
-        <v>1.061443518284256</v>
+        <v>1.073951978395448</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.895563051618568</v>
+        <v>6.640171827484546</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09195175828270097</v>
+        <v>0.09185105073076817</v>
       </c>
       <c r="C29">
-        <v>181.7045986297982</v>
+        <v>179.6926836501027</v>
       </c>
       <c r="D29">
-        <v>241.2715986297982</v>
+        <v>241.6006836501027</v>
       </c>
       <c r="E29">
-        <v>-5.992999999999995</v>
+        <v>-3.651999999999987</v>
       </c>
       <c r="F29">
-        <v>63.20700000000001</v>
+        <v>65.54800000000002</v>
       </c>
       <c r="G29">
         <v>3.64</v>
@@ -3665,28 +3665,28 @@
         <v>22.79</v>
       </c>
       <c r="M29">
-        <v>3.432140100000001</v>
+        <v>3.559256400000001</v>
       </c>
       <c r="N29">
-        <v>19.3578599</v>
+        <v>19.2307436</v>
       </c>
       <c r="O29">
-        <v>3.484414782</v>
+        <v>3.461533847999999</v>
       </c>
       <c r="P29">
-        <v>15.873445118</v>
+        <v>15.769209752</v>
       </c>
       <c r="Q29">
-        <v>21.083445118</v>
+        <v>20.979209752</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1094927921680835</v>
+        <v>0.1102552371260669</v>
       </c>
       <c r="T29">
-        <v>1.073951978395448</v>
+        <v>1.08680789573195</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.640171827484546</v>
+        <v>6.403022833645812</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09185105073076817</v>
+        <v>0.09175034317883538</v>
       </c>
       <c r="C30">
-        <v>179.6926836501027</v>
+        <v>177.6816676147152</v>
       </c>
       <c r="D30">
-        <v>241.6006836501027</v>
+        <v>241.9306676147152</v>
       </c>
       <c r="E30">
-        <v>-3.651999999999987</v>
+        <v>-1.310999999999993</v>
       </c>
       <c r="F30">
-        <v>65.54800000000002</v>
+        <v>67.88900000000001</v>
       </c>
       <c r="G30">
         <v>3.64</v>
@@ -3747,28 +3747,28 @@
         <v>22.79</v>
       </c>
       <c r="M30">
-        <v>3.559256400000001</v>
+        <v>3.686372700000001</v>
       </c>
       <c r="N30">
-        <v>19.2307436</v>
+        <v>19.1036273</v>
       </c>
       <c r="O30">
-        <v>3.461533847999999</v>
+        <v>3.438652914</v>
       </c>
       <c r="P30">
-        <v>15.769209752</v>
+        <v>15.664974386</v>
       </c>
       <c r="Q30">
-        <v>20.979209752</v>
+        <v>20.874974386</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1102552371260669</v>
+        <v>0.1110391594068104</v>
       </c>
       <c r="T30">
-        <v>1.08680789573195</v>
+        <v>1.100025951584973</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.403022833645812</v>
+        <v>6.182228942830441</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09175034317883538</v>
+        <v>0.09189563562690257</v>
       </c>
       <c r="C31">
-        <v>177.6816676147152</v>
+        <v>174.8648816026706</v>
       </c>
       <c r="D31">
-        <v>241.9306676147152</v>
+        <v>241.4548816026706</v>
       </c>
       <c r="E31">
-        <v>-1.311000000000007</v>
+        <v>1.030000000000001</v>
       </c>
       <c r="F31">
-        <v>67.889</v>
+        <v>70.23</v>
       </c>
       <c r="G31">
         <v>3.64</v>
@@ -3829,45 +3829,45 @@
         <v>22.79</v>
       </c>
       <c r="M31">
-        <v>3.6863727</v>
+        <v>3.883719</v>
       </c>
       <c r="N31">
-        <v>19.1036273</v>
+        <v>18.906281</v>
       </c>
       <c r="O31">
-        <v>3.438652914</v>
+        <v>3.40313058</v>
       </c>
       <c r="P31">
-        <v>15.664974386</v>
+        <v>15.50315042</v>
       </c>
       <c r="Q31">
-        <v>20.874974386</v>
+        <v>20.71315042</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1110391594068104</v>
+        <v>0.1118454794670037</v>
       </c>
       <c r="T31">
-        <v>1.100025951584973</v>
+        <v>1.113621666176654</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.18</v>
       </c>
       <c r="W31">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.182228942830442</v>
+        <v>5.868086748809581</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09189563562690257</v>
+        <v>0.09180312807496979</v>
       </c>
       <c r="C32">
-        <v>174.8648816026706</v>
+        <v>172.8265973569589</v>
       </c>
       <c r="D32">
-        <v>241.4548816026706</v>
+        <v>241.7575973569589</v>
       </c>
       <c r="E32">
-        <v>1.030000000000001</v>
+        <v>3.371000000000009</v>
       </c>
       <c r="F32">
-        <v>70.23</v>
+        <v>72.57100000000001</v>
       </c>
       <c r="G32">
         <v>3.64</v>
@@ -3911,28 +3911,28 @@
         <v>22.79</v>
       </c>
       <c r="M32">
-        <v>3.883719</v>
+        <v>4.0131763</v>
       </c>
       <c r="N32">
-        <v>18.906281</v>
+        <v>18.7768237</v>
       </c>
       <c r="O32">
-        <v>3.40313058</v>
+        <v>3.379828266</v>
       </c>
       <c r="P32">
-        <v>15.50315042</v>
+        <v>15.396995434</v>
       </c>
       <c r="Q32">
-        <v>20.71315042</v>
+        <v>20.606995434</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1118454794670037</v>
+        <v>0.1126751711231446</v>
       </c>
       <c r="T32">
-        <v>1.113621666176654</v>
+        <v>1.127611459452152</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.868086748809581</v>
+        <v>5.678793627880239</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09180312807496979</v>
+        <v>0.091710620523037</v>
       </c>
       <c r="C33">
-        <v>172.8265973569589</v>
+        <v>170.7890731029942</v>
       </c>
       <c r="D33">
-        <v>241.7575973569589</v>
+        <v>242.0610731029942</v>
       </c>
       <c r="E33">
-        <v>3.371000000000009</v>
+        <v>5.712000000000003</v>
       </c>
       <c r="F33">
-        <v>72.57100000000001</v>
+        <v>74.91200000000001</v>
       </c>
       <c r="G33">
         <v>3.64</v>
@@ -3993,28 +3993,28 @@
         <v>22.79</v>
       </c>
       <c r="M33">
-        <v>4.0131763</v>
+        <v>4.142633600000001</v>
       </c>
       <c r="N33">
-        <v>18.7768237</v>
+        <v>18.6473664</v>
       </c>
       <c r="O33">
-        <v>3.379828266</v>
+        <v>3.356525952</v>
       </c>
       <c r="P33">
-        <v>15.396995434</v>
+        <v>15.290840448</v>
       </c>
       <c r="Q33">
-        <v>20.606995434</v>
+        <v>20.500840448</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1126751711231446</v>
+        <v>0.1135292654750544</v>
       </c>
       <c r="T33">
-        <v>1.127611459452152</v>
+        <v>1.142012717235753</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.678793627880239</v>
+        <v>5.501331327008982</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.091710620523037</v>
+        <v>0.0916181129711042</v>
       </c>
       <c r="C34">
-        <v>170.7890731029942</v>
+        <v>168.7523117064023</v>
       </c>
       <c r="D34">
-        <v>242.0610731029942</v>
+        <v>242.3653117064023</v>
       </c>
       <c r="E34">
-        <v>5.712000000000003</v>
+        <v>8.053000000000011</v>
       </c>
       <c r="F34">
-        <v>74.91200000000001</v>
+        <v>77.25300000000001</v>
       </c>
       <c r="G34">
         <v>3.64</v>
@@ -4075,28 +4075,28 @@
         <v>22.79</v>
       </c>
       <c r="M34">
-        <v>4.142633600000001</v>
+        <v>4.272090900000001</v>
       </c>
       <c r="N34">
-        <v>18.6473664</v>
+        <v>18.5179091</v>
       </c>
       <c r="O34">
-        <v>3.356525952</v>
+        <v>3.333223637999999</v>
       </c>
       <c r="P34">
-        <v>15.290840448</v>
+        <v>15.184685462</v>
       </c>
       <c r="Q34">
-        <v>20.500840448</v>
+        <v>20.394685462</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1135292654750544</v>
+        <v>0.1144088551807525</v>
       </c>
       <c r="T34">
-        <v>1.142012717235753</v>
+        <v>1.156843863311402</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.501331327008982</v>
+        <v>5.334624317099618</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0916181129711042</v>
+        <v>0.0915256054191714</v>
       </c>
       <c r="C35">
-        <v>168.7523117064023</v>
+        <v>166.7163160472341</v>
       </c>
       <c r="D35">
-        <v>242.3653117064023</v>
+        <v>242.6703160472341</v>
       </c>
       <c r="E35">
-        <v>8.053000000000011</v>
+        <v>10.39400000000001</v>
       </c>
       <c r="F35">
-        <v>77.25300000000001</v>
+        <v>79.59400000000001</v>
       </c>
       <c r="G35">
         <v>3.64</v>
@@ -4157,28 +4157,28 @@
         <v>22.79</v>
       </c>
       <c r="M35">
-        <v>4.272090900000001</v>
+        <v>4.401548200000001</v>
       </c>
       <c r="N35">
-        <v>18.5179091</v>
+        <v>18.3884518</v>
       </c>
       <c r="O35">
-        <v>3.333223637999999</v>
+        <v>3.309921324</v>
       </c>
       <c r="P35">
-        <v>15.184685462</v>
+        <v>15.078530476</v>
       </c>
       <c r="Q35">
-        <v>20.394685462</v>
+        <v>20.288530476</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1144088551807525</v>
+        <v>0.1153150991199567</v>
       </c>
       <c r="T35">
-        <v>1.156843863311402</v>
+        <v>1.17212443805601</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.334624317099618</v>
+        <v>5.177723601890807</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0915256054191714</v>
+        <v>0.09143309786723861</v>
       </c>
       <c r="C36">
-        <v>166.7163160472341</v>
+        <v>164.6810890200563</v>
       </c>
       <c r="D36">
-        <v>242.6703160472341</v>
+        <v>242.9760890200563</v>
       </c>
       <c r="E36">
-        <v>10.39400000000001</v>
+        <v>12.73500000000001</v>
       </c>
       <c r="F36">
-        <v>79.59400000000001</v>
+        <v>81.93500000000002</v>
       </c>
       <c r="G36">
         <v>3.64</v>
@@ -4239,28 +4239,28 @@
         <v>22.79</v>
       </c>
       <c r="M36">
-        <v>4.401548200000001</v>
+        <v>4.531005500000001</v>
       </c>
       <c r="N36">
-        <v>18.3884518</v>
+        <v>18.2589945</v>
       </c>
       <c r="O36">
-        <v>3.309921324</v>
+        <v>3.28661901</v>
       </c>
       <c r="P36">
-        <v>15.078530476</v>
+        <v>14.97237549</v>
       </c>
       <c r="Q36">
-        <v>20.288530476</v>
+        <v>20.18237549</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1153150991199567</v>
+        <v>0.1162492274880594</v>
       </c>
       <c r="T36">
-        <v>1.17212443805601</v>
+        <v>1.187875184331221</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.177723601890807</v>
+        <v>5.029788641836784</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09143309786723861</v>
+        <v>0.09134059031530581</v>
       </c>
       <c r="C37">
-        <v>164.6810890200563</v>
+        <v>162.646633534043</v>
       </c>
       <c r="D37">
-        <v>242.9760890200563</v>
+        <v>243.2826335340431</v>
       </c>
       <c r="E37">
-        <v>12.73500000000001</v>
+        <v>15.07600000000002</v>
       </c>
       <c r="F37">
-        <v>81.93500000000002</v>
+        <v>84.27600000000002</v>
       </c>
       <c r="G37">
         <v>3.64</v>
@@ -4321,28 +4321,28 @@
         <v>22.79</v>
       </c>
       <c r="M37">
-        <v>4.531005500000001</v>
+        <v>4.660462800000001</v>
       </c>
       <c r="N37">
-        <v>18.2589945</v>
+        <v>18.1295372</v>
       </c>
       <c r="O37">
-        <v>3.28661901</v>
+        <v>3.263316696</v>
       </c>
       <c r="P37">
-        <v>14.97237549</v>
+        <v>14.866220504</v>
       </c>
       <c r="Q37">
-        <v>20.18237549</v>
+        <v>20.076220504</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1162492274880594</v>
+        <v>0.1172125473676653</v>
       </c>
       <c r="T37">
-        <v>1.187875184331221</v>
+        <v>1.204118141427532</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.029788641836784</v>
+        <v>4.890072290674651</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09134059031530582</v>
+        <v>0.09124808276337303</v>
       </c>
       <c r="C38">
-        <v>162.646633534043</v>
+        <v>160.6129525130683</v>
       </c>
       <c r="D38">
-        <v>243.282633534043</v>
+        <v>243.5899525130683</v>
       </c>
       <c r="E38">
-        <v>15.07600000000001</v>
+        <v>17.417</v>
       </c>
       <c r="F38">
-        <v>84.27600000000001</v>
+        <v>86.617</v>
       </c>
       <c r="G38">
         <v>3.64</v>
@@ -4403,28 +4403,28 @@
         <v>22.79</v>
       </c>
       <c r="M38">
-        <v>4.6604628</v>
+        <v>4.789920100000001</v>
       </c>
       <c r="N38">
-        <v>18.1295372</v>
+        <v>18.0000799</v>
       </c>
       <c r="O38">
-        <v>3.263316696</v>
+        <v>3.240014382</v>
       </c>
       <c r="P38">
-        <v>14.866220504</v>
+        <v>14.760065518</v>
       </c>
       <c r="Q38">
-        <v>20.076220504</v>
+        <v>19.970065518</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1172125473676653</v>
+        <v>0.1182064488307508</v>
       </c>
       <c r="T38">
-        <v>1.204118141427532</v>
+        <v>1.220876747955472</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.890072290674651</v>
+        <v>4.757908174710471</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09124808276337303</v>
+        <v>0.09115557521144022</v>
       </c>
       <c r="C39">
-        <v>160.6129525130683</v>
+        <v>158.5800488957984</v>
       </c>
       <c r="D39">
-        <v>243.5899525130683</v>
+        <v>243.8980488957984</v>
       </c>
       <c r="E39">
-        <v>17.417</v>
+        <v>19.75800000000001</v>
       </c>
       <c r="F39">
-        <v>86.617</v>
+        <v>88.95800000000001</v>
       </c>
       <c r="G39">
         <v>3.64</v>
@@ -4485,28 +4485,28 @@
         <v>22.79</v>
       </c>
       <c r="M39">
-        <v>4.789920100000001</v>
+        <v>4.919377400000001</v>
       </c>
       <c r="N39">
-        <v>18.0000799</v>
+        <v>17.8706226</v>
       </c>
       <c r="O39">
-        <v>3.240014382</v>
+        <v>3.216712067999999</v>
       </c>
       <c r="P39">
-        <v>14.760065518</v>
+        <v>14.653910532</v>
       </c>
       <c r="Q39">
-        <v>19.970065518</v>
+        <v>19.863910532</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1182064488307508</v>
+        <v>0.1192324116313552</v>
       </c>
       <c r="T39">
-        <v>1.220876747955472</v>
+        <v>1.238175954693991</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.757908174710471</v>
+        <v>4.632700064849669</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09115557521144022</v>
+        <v>0.09106306765950742</v>
       </c>
       <c r="C40">
-        <v>158.5800488957984</v>
+        <v>156.5479256357862</v>
       </c>
       <c r="D40">
-        <v>243.8980488957984</v>
+        <v>244.2069256357863</v>
       </c>
       <c r="E40">
-        <v>19.75800000000001</v>
+        <v>22.099</v>
       </c>
       <c r="F40">
-        <v>88.95800000000001</v>
+        <v>91.29900000000001</v>
       </c>
       <c r="G40">
         <v>3.64</v>
@@ -4567,28 +4567,28 @@
         <v>22.79</v>
       </c>
       <c r="M40">
-        <v>4.919377400000001</v>
+        <v>5.0488347</v>
       </c>
       <c r="N40">
-        <v>17.8706226</v>
+        <v>17.7411653</v>
       </c>
       <c r="O40">
-        <v>3.216712067999999</v>
+        <v>3.193409754</v>
       </c>
       <c r="P40">
-        <v>14.653910532</v>
+        <v>14.547755546</v>
       </c>
       <c r="Q40">
-        <v>19.863910532</v>
+        <v>19.757755546</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1192324116313552</v>
+        <v>0.1202920125565695</v>
       </c>
       <c r="T40">
-        <v>1.238175954693991</v>
+        <v>1.256042348538691</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.632700064849669</v>
+        <v>4.513912883699678</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09106306765950742</v>
+        <v>0.09179056010757464</v>
       </c>
       <c r="C41">
-        <v>156.5479256357862</v>
+        <v>151.7987825399994</v>
       </c>
       <c r="D41">
-        <v>244.2069256357863</v>
+        <v>241.7987825399994</v>
       </c>
       <c r="E41">
-        <v>22.099</v>
+        <v>24.44000000000001</v>
       </c>
       <c r="F41">
-        <v>91.29900000000001</v>
+        <v>93.64000000000001</v>
       </c>
       <c r="G41">
         <v>3.64</v>
@@ -4649,45 +4649,45 @@
         <v>22.79</v>
       </c>
       <c r="M41">
-        <v>5.0488347</v>
+        <v>5.412392000000001</v>
       </c>
       <c r="N41">
-        <v>17.7411653</v>
+        <v>17.377608</v>
       </c>
       <c r="O41">
-        <v>3.193409754</v>
+        <v>3.12796944</v>
       </c>
       <c r="P41">
-        <v>14.547755546</v>
+        <v>14.24963856</v>
       </c>
       <c r="Q41">
-        <v>19.757755546</v>
+        <v>19.45963856</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1202920125565695</v>
+        <v>0.1213869335126244</v>
       </c>
       <c r="T41">
-        <v>1.256042348538691</v>
+        <v>1.274504288844881</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.18</v>
       </c>
       <c r="W41">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.513912883699678</v>
+        <v>4.210707576243553</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09179056010757464</v>
+        <v>0.09171855255564183</v>
       </c>
       <c r="C42">
-        <v>151.7987825399994</v>
+        <v>149.6940218047359</v>
       </c>
       <c r="D42">
-        <v>241.7987825399994</v>
+        <v>242.0350218047359</v>
       </c>
       <c r="E42">
-        <v>24.44000000000001</v>
+        <v>26.78100000000002</v>
       </c>
       <c r="F42">
-        <v>93.64000000000001</v>
+        <v>95.98100000000002</v>
       </c>
       <c r="G42">
         <v>3.64</v>
@@ -4731,28 +4731,28 @@
         <v>22.79</v>
       </c>
       <c r="M42">
-        <v>5.412392000000001</v>
+        <v>5.547701800000001</v>
       </c>
       <c r="N42">
-        <v>17.377608</v>
+        <v>17.2422982</v>
       </c>
       <c r="O42">
-        <v>3.12796944</v>
+        <v>3.103613675999999</v>
       </c>
       <c r="P42">
-        <v>14.24963856</v>
+        <v>14.138684524</v>
       </c>
       <c r="Q42">
-        <v>19.45963856</v>
+        <v>19.348684524</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1213869335126244</v>
+        <v>0.1225189704332912</v>
       </c>
       <c r="T42">
-        <v>1.274504288844881</v>
+        <v>1.293592057636027</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.210707576243553</v>
+        <v>4.108007391457124</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09171855255564183</v>
+        <v>0.09164654500370903</v>
       </c>
       <c r="C43">
-        <v>149.6940218047359</v>
+        <v>147.5897231360615</v>
       </c>
       <c r="D43">
-        <v>242.0350218047359</v>
+        <v>242.2717231360616</v>
       </c>
       <c r="E43">
-        <v>26.78100000000002</v>
+        <v>29.12200000000001</v>
       </c>
       <c r="F43">
-        <v>95.98100000000002</v>
+        <v>98.32200000000002</v>
       </c>
       <c r="G43">
         <v>3.64</v>
@@ -4813,28 +4813,28 @@
         <v>22.79</v>
       </c>
       <c r="M43">
-        <v>5.547701800000001</v>
+        <v>5.683011600000001</v>
       </c>
       <c r="N43">
-        <v>17.2422982</v>
+        <v>17.1069884</v>
       </c>
       <c r="O43">
-        <v>3.103613675999999</v>
+        <v>3.079257912</v>
       </c>
       <c r="P43">
-        <v>14.138684524</v>
+        <v>14.027730488</v>
       </c>
       <c r="Q43">
-        <v>19.348684524</v>
+        <v>19.237730488</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1225189704332912</v>
+        <v>0.1236900431098432</v>
       </c>
       <c r="T43">
-        <v>1.293592057636027</v>
+        <v>1.313338025351005</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.108007391457124</v>
+        <v>4.010197691660526</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09164654500370904</v>
+        <v>0.09280863745177624</v>
       </c>
       <c r="C44">
-        <v>147.5897231360615</v>
+        <v>141.4843992946859</v>
       </c>
       <c r="D44">
-        <v>242.2717231360615</v>
+        <v>238.5073992946859</v>
       </c>
       <c r="E44">
-        <v>29.122</v>
+        <v>31.46300000000001</v>
       </c>
       <c r="F44">
-        <v>98.322</v>
+        <v>100.663</v>
       </c>
       <c r="G44">
         <v>3.64</v>
@@ -4895,45 +4895,45 @@
         <v>22.79</v>
       </c>
       <c r="M44">
-        <v>5.6830116</v>
+        <v>6.170641900000001</v>
       </c>
       <c r="N44">
-        <v>17.1069884</v>
+        <v>16.6193581</v>
       </c>
       <c r="O44">
-        <v>3.079257912</v>
+        <v>2.991484458</v>
       </c>
       <c r="P44">
-        <v>14.027730488</v>
+        <v>13.627873642</v>
       </c>
       <c r="Q44">
-        <v>19.237730488</v>
+        <v>18.837873642</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1236900431098432</v>
+        <v>0.1249022060557478</v>
       </c>
       <c r="T44">
-        <v>1.313338025351005</v>
+        <v>1.333776834038439</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.18</v>
       </c>
       <c r="W44">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.010197691660527</v>
+        <v>3.693294858027655</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09280863745177624</v>
+        <v>0.09276532989984346</v>
       </c>
       <c r="C45">
-        <v>141.4843992946859</v>
+        <v>139.2815842011287</v>
       </c>
       <c r="D45">
-        <v>238.5073992946859</v>
+        <v>238.6455842011288</v>
       </c>
       <c r="E45">
-        <v>31.46300000000001</v>
+        <v>33.804</v>
       </c>
       <c r="F45">
-        <v>100.663</v>
+        <v>103.004</v>
       </c>
       <c r="G45">
         <v>3.64</v>
@@ -4977,28 +4977,28 @@
         <v>22.79</v>
       </c>
       <c r="M45">
-        <v>6.170641900000001</v>
+        <v>6.3141452</v>
       </c>
       <c r="N45">
-        <v>16.6193581</v>
+        <v>16.4758548</v>
       </c>
       <c r="O45">
-        <v>2.991484458</v>
+        <v>2.965653864</v>
       </c>
       <c r="P45">
-        <v>13.627873642</v>
+        <v>13.510200936</v>
       </c>
       <c r="Q45">
-        <v>18.837873642</v>
+        <v>18.720200936</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1249022060557478</v>
+        <v>0.1261576605354347</v>
       </c>
       <c r="T45">
-        <v>1.333776834038439</v>
+        <v>1.354945600178995</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.693294858027655</v>
+        <v>3.609356338527026</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09276532989984346</v>
+        <v>0.09272202234791066</v>
       </c>
       <c r="C46">
-        <v>139.2815842011287</v>
+        <v>137.0789293217873</v>
       </c>
       <c r="D46">
-        <v>238.6455842011288</v>
+        <v>238.7839293217874</v>
       </c>
       <c r="E46">
-        <v>33.804</v>
+        <v>36.14500000000001</v>
       </c>
       <c r="F46">
-        <v>103.004</v>
+        <v>105.345</v>
       </c>
       <c r="G46">
         <v>3.64</v>
@@ -5059,28 +5059,28 @@
         <v>22.79</v>
       </c>
       <c r="M46">
-        <v>6.3141452</v>
+        <v>6.457648500000001</v>
       </c>
       <c r="N46">
-        <v>16.4758548</v>
+        <v>16.3323515</v>
       </c>
       <c r="O46">
-        <v>2.965653864</v>
+        <v>2.939823269999999</v>
       </c>
       <c r="P46">
-        <v>13.510200936</v>
+        <v>13.39252823</v>
       </c>
       <c r="Q46">
-        <v>18.720200936</v>
+        <v>18.60252823</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1261576605354347</v>
+        <v>0.1274587679052921</v>
       </c>
       <c r="T46">
-        <v>1.354945600178995</v>
+        <v>1.376884139633753</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.609356338527026</v>
+        <v>3.529148419893092</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09272202234791066</v>
+        <v>0.09373487479597786</v>
       </c>
       <c r="C47">
-        <v>137.0789293217873</v>
+        <v>131.5438219223515</v>
       </c>
       <c r="D47">
-        <v>238.7839293217874</v>
+        <v>235.5898219223515</v>
       </c>
       <c r="E47">
-        <v>36.14500000000001</v>
+        <v>38.48600000000002</v>
       </c>
       <c r="F47">
-        <v>105.345</v>
+        <v>107.686</v>
       </c>
       <c r="G47">
         <v>3.64</v>
@@ -5141,45 +5141,45 @@
         <v>22.79</v>
       </c>
       <c r="M47">
-        <v>6.457648500000001</v>
+        <v>6.902672600000002</v>
       </c>
       <c r="N47">
-        <v>16.3323515</v>
+        <v>15.8873274</v>
       </c>
       <c r="O47">
-        <v>2.939823269999999</v>
+        <v>2.859718931999999</v>
       </c>
       <c r="P47">
-        <v>13.39252823</v>
+        <v>13.027608468</v>
       </c>
       <c r="Q47">
-        <v>18.60252823</v>
+        <v>18.237608468</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1274587679052921</v>
+        <v>0.128808064436996</v>
       </c>
       <c r="T47">
-        <v>1.376884139633753</v>
+        <v>1.399635217586836</v>
       </c>
       <c r="U47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.18</v>
       </c>
       <c r="W47">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.529148419893092</v>
+        <v>3.301619723351792</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09373487479597786</v>
+        <v>0.09371452724404507</v>
       </c>
       <c r="C48">
-        <v>131.5438219223515</v>
+        <v>129.266148154672</v>
       </c>
       <c r="D48">
-        <v>235.5898219223515</v>
+        <v>235.653148154672</v>
       </c>
       <c r="E48">
-        <v>38.48600000000002</v>
+        <v>40.82700000000001</v>
       </c>
       <c r="F48">
-        <v>107.686</v>
+        <v>110.027</v>
       </c>
       <c r="G48">
         <v>3.64</v>
@@ -5223,28 +5223,28 @@
         <v>22.79</v>
       </c>
       <c r="M48">
-        <v>6.902672600000002</v>
+        <v>7.052730700000001</v>
       </c>
       <c r="N48">
-        <v>15.8873274</v>
+        <v>15.7372693</v>
       </c>
       <c r="O48">
-        <v>2.859718931999999</v>
+        <v>2.832708473999999</v>
       </c>
       <c r="P48">
-        <v>13.027608468</v>
+        <v>12.904560826</v>
       </c>
       <c r="Q48">
-        <v>18.237608468</v>
+        <v>18.114560826</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.128808064436996</v>
+        <v>0.1302082778189529</v>
       </c>
       <c r="T48">
-        <v>1.399635217586836</v>
+        <v>1.423244826783431</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.301619723351792</v>
+        <v>3.231372495195371</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09371452724404507</v>
+        <v>0.09369417969211227</v>
       </c>
       <c r="C49">
-        <v>129.266148154672</v>
+        <v>126.9885084401607</v>
       </c>
       <c r="D49">
-        <v>235.653148154672</v>
+        <v>235.7165084401607</v>
       </c>
       <c r="E49">
-        <v>40.82700000000001</v>
+        <v>43.16800000000002</v>
       </c>
       <c r="F49">
-        <v>110.027</v>
+        <v>112.368</v>
       </c>
       <c r="G49">
         <v>3.64</v>
@@ -5305,28 +5305,28 @@
         <v>22.79</v>
       </c>
       <c r="M49">
-        <v>7.052730700000001</v>
+        <v>7.202788800000002</v>
       </c>
       <c r="N49">
-        <v>15.7372693</v>
+        <v>15.5872112</v>
       </c>
       <c r="O49">
-        <v>2.832708473999999</v>
+        <v>2.805698015999999</v>
       </c>
       <c r="P49">
-        <v>12.904560826</v>
+        <v>12.781513184</v>
       </c>
       <c r="Q49">
-        <v>18.114560826</v>
+        <v>17.991513184</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1302082778189529</v>
+        <v>0.1316623455617544</v>
       </c>
       <c r="T49">
-        <v>1.423244826783431</v>
+        <v>1.447762497872203</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.231372495195371</v>
+        <v>3.1640522348788</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09369417969211227</v>
+        <v>0.09367383214017946</v>
       </c>
       <c r="C50">
-        <v>126.9885084401607</v>
+        <v>124.710902806293</v>
       </c>
       <c r="D50">
-        <v>235.7165084401607</v>
+        <v>235.779902806293</v>
       </c>
       <c r="E50">
-        <v>43.16800000000001</v>
+        <v>45.509</v>
       </c>
       <c r="F50">
-        <v>112.368</v>
+        <v>114.709</v>
       </c>
       <c r="G50">
         <v>3.64</v>
@@ -5387,28 +5387,28 @@
         <v>22.79</v>
       </c>
       <c r="M50">
-        <v>7.202788800000001</v>
+        <v>7.3528469</v>
       </c>
       <c r="N50">
-        <v>15.5872112</v>
+        <v>15.4371531</v>
       </c>
       <c r="O50">
-        <v>2.805698016</v>
+        <v>2.778687558</v>
       </c>
       <c r="P50">
-        <v>12.781513184</v>
+        <v>12.658465542</v>
       </c>
       <c r="Q50">
-        <v>17.991513184</v>
+        <v>17.868465542</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1316623455617544</v>
+        <v>0.1331734355689793</v>
       </c>
       <c r="T50">
-        <v>1.447762497872203</v>
+        <v>1.473241646258573</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.164052234878801</v>
+        <v>3.099479740289438</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09367383214017946</v>
+        <v>0.09365348458824667</v>
       </c>
       <c r="C51">
-        <v>124.710902806293</v>
+        <v>122.4333312805732</v>
       </c>
       <c r="D51">
-        <v>235.779902806293</v>
+        <v>235.8433312805733</v>
       </c>
       <c r="E51">
-        <v>45.509</v>
+        <v>47.85000000000001</v>
       </c>
       <c r="F51">
-        <v>114.709</v>
+        <v>117.05</v>
       </c>
       <c r="G51">
         <v>3.64</v>
@@ -5469,28 +5469,28 @@
         <v>22.79</v>
       </c>
       <c r="M51">
-        <v>7.3528469</v>
+        <v>7.502905000000001</v>
       </c>
       <c r="N51">
-        <v>15.4371531</v>
+        <v>15.287095</v>
       </c>
       <c r="O51">
-        <v>2.778687558</v>
+        <v>2.751677099999999</v>
       </c>
       <c r="P51">
-        <v>12.658465542</v>
+        <v>12.5354179</v>
       </c>
       <c r="Q51">
-        <v>17.868465542</v>
+        <v>17.7454179</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1331734355689793</v>
+        <v>0.1347449691764933</v>
       </c>
       <c r="T51">
-        <v>1.473241646258573</v>
+        <v>1.499739960580399</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.099479740289438</v>
+        <v>3.037490145483649</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09365348458824667</v>
+        <v>0.09689509703631388</v>
       </c>
       <c r="C52">
-        <v>122.4333312805732</v>
+        <v>110.4000712817178</v>
       </c>
       <c r="D52">
-        <v>235.8433312805733</v>
+        <v>226.1510712817179</v>
       </c>
       <c r="E52">
-        <v>47.85000000000001</v>
+        <v>50.19100000000002</v>
       </c>
       <c r="F52">
-        <v>117.05</v>
+        <v>119.391</v>
       </c>
       <c r="G52">
         <v>3.64</v>
@@ -5551,45 +5551,45 @@
         <v>22.79</v>
       </c>
       <c r="M52">
-        <v>7.502905000000001</v>
+        <v>8.584212900000002</v>
       </c>
       <c r="N52">
-        <v>15.287095</v>
+        <v>14.2057871</v>
       </c>
       <c r="O52">
-        <v>2.751677099999999</v>
+        <v>2.557041677999999</v>
       </c>
       <c r="P52">
-        <v>12.5354179</v>
+        <v>11.648745422</v>
       </c>
       <c r="Q52">
-        <v>17.7454179</v>
+        <v>16.858745422</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1347449691764933</v>
+        <v>0.1363806470128855</v>
       </c>
       <c r="T52">
-        <v>1.499739960580399</v>
+        <v>1.527319838752095</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.18</v>
       </c>
       <c r="W52">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.037490145483649</v>
+        <v>2.654873576120181</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09689509703631388</v>
+        <v>0.09693870948438109</v>
       </c>
       <c r="C53">
-        <v>110.4000712817178</v>
+        <v>107.9341002310811</v>
       </c>
       <c r="D53">
-        <v>226.1510712817179</v>
+        <v>226.0261002310812</v>
       </c>
       <c r="E53">
-        <v>50.19100000000002</v>
+        <v>52.53200000000001</v>
       </c>
       <c r="F53">
-        <v>119.391</v>
+        <v>121.732</v>
       </c>
       <c r="G53">
         <v>3.64</v>
@@ -5633,28 +5633,28 @@
         <v>22.79</v>
       </c>
       <c r="M53">
-        <v>8.584212900000002</v>
+        <v>8.752530800000002</v>
       </c>
       <c r="N53">
-        <v>14.2057871</v>
+        <v>14.0374692</v>
       </c>
       <c r="O53">
-        <v>2.557041677999999</v>
+        <v>2.526744455999999</v>
       </c>
       <c r="P53">
-        <v>11.648745422</v>
+        <v>11.510724744</v>
       </c>
       <c r="Q53">
-        <v>16.858745422</v>
+        <v>16.720724744</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1363806470128855</v>
+        <v>0.1380844780924606</v>
       </c>
       <c r="T53">
-        <v>1.527319838752095</v>
+        <v>1.556048878514279</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.654873576120181</v>
+        <v>2.603818315040947</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09693870948438109</v>
+        <v>0.0969823219324483</v>
       </c>
       <c r="C54">
-        <v>107.9341002310811</v>
+        <v>105.4682672221331</v>
       </c>
       <c r="D54">
-        <v>226.0261002310812</v>
+        <v>225.9012672221332</v>
       </c>
       <c r="E54">
-        <v>52.53200000000001</v>
+        <v>54.87300000000002</v>
       </c>
       <c r="F54">
-        <v>121.732</v>
+        <v>124.073</v>
       </c>
       <c r="G54">
         <v>3.64</v>
@@ -5715,28 +5715,28 @@
         <v>22.79</v>
       </c>
       <c r="M54">
-        <v>8.752530800000002</v>
+        <v>8.920848700000002</v>
       </c>
       <c r="N54">
-        <v>14.0374692</v>
+        <v>13.8691513</v>
       </c>
       <c r="O54">
-        <v>2.526744455999999</v>
+        <v>2.496447233999999</v>
       </c>
       <c r="P54">
-        <v>11.510724744</v>
+        <v>11.372704066</v>
       </c>
       <c r="Q54">
-        <v>16.720724744</v>
+        <v>16.582704066</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1380844780924606</v>
+        <v>0.1398608126222304</v>
       </c>
       <c r="T54">
-        <v>1.556048878514279</v>
+        <v>1.586000430606768</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.603818315040947</v>
+        <v>2.554689667587344</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0969823219324483</v>
+        <v>0.09702593438051549</v>
       </c>
       <c r="C55">
-        <v>105.4682672221331</v>
+        <v>103.002572026281</v>
       </c>
       <c r="D55">
-        <v>225.9012672221332</v>
+        <v>225.7765720262811</v>
       </c>
       <c r="E55">
-        <v>54.87300000000002</v>
+        <v>57.21400000000001</v>
       </c>
       <c r="F55">
-        <v>124.073</v>
+        <v>126.414</v>
       </c>
       <c r="G55">
         <v>3.64</v>
@@ -5797,28 +5797,28 @@
         <v>22.79</v>
       </c>
       <c r="M55">
-        <v>8.920848700000002</v>
+        <v>9.089166600000002</v>
       </c>
       <c r="N55">
-        <v>13.8691513</v>
+        <v>13.7008334</v>
       </c>
       <c r="O55">
-        <v>2.496447233999999</v>
+        <v>2.466150012</v>
       </c>
       <c r="P55">
-        <v>11.372704066</v>
+        <v>11.234683388</v>
       </c>
       <c r="Q55">
-        <v>16.582704066</v>
+        <v>16.444683388</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1398608126222304</v>
+        <v>0.1417143790880772</v>
       </c>
       <c r="T55">
-        <v>1.586000430606768</v>
+        <v>1.617254224094582</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.554689667587344</v>
+        <v>2.507380599669061</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09702593438051549</v>
+        <v>0.09882844682858269</v>
       </c>
       <c r="C56">
-        <v>103.002572026281</v>
+        <v>95.62562526485368</v>
       </c>
       <c r="D56">
-        <v>225.7765720262811</v>
+        <v>220.7406252648537</v>
       </c>
       <c r="E56">
-        <v>57.21400000000001</v>
+        <v>59.55500000000002</v>
       </c>
       <c r="F56">
-        <v>126.414</v>
+        <v>128.755</v>
       </c>
       <c r="G56">
         <v>3.64</v>
@@ -5879,45 +5879,45 @@
         <v>22.79</v>
       </c>
       <c r="M56">
-        <v>9.089166600000002</v>
+        <v>9.759629000000002</v>
       </c>
       <c r="N56">
-        <v>13.7008334</v>
+        <v>13.030371</v>
       </c>
       <c r="O56">
-        <v>2.466150012</v>
+        <v>2.345466779999999</v>
       </c>
       <c r="P56">
-        <v>11.234683388</v>
+        <v>10.68490422</v>
       </c>
       <c r="Q56">
-        <v>16.444683388</v>
+        <v>15.89490422</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1417143790880772</v>
+        <v>0.1436503262857393</v>
       </c>
       <c r="T56">
-        <v>1.617254224094582</v>
+        <v>1.649897075070744</v>
       </c>
       <c r="U56">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.18</v>
       </c>
       <c r="W56">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.507380599669061</v>
+        <v>2.335129747247564</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09882844682858269</v>
+        <v>0.0989040392766499</v>
       </c>
       <c r="C57">
-        <v>95.62562526485368</v>
+        <v>93.07833505982578</v>
       </c>
       <c r="D57">
-        <v>220.7406252648537</v>
+        <v>220.5343350598258</v>
       </c>
       <c r="E57">
-        <v>59.55500000000002</v>
+        <v>61.89600000000003</v>
       </c>
       <c r="F57">
-        <v>128.755</v>
+        <v>131.096</v>
       </c>
       <c r="G57">
         <v>3.64</v>
@@ -5961,28 +5961,28 @@
         <v>22.79</v>
       </c>
       <c r="M57">
-        <v>9.759629000000002</v>
+        <v>9.937076800000003</v>
       </c>
       <c r="N57">
-        <v>13.030371</v>
+        <v>12.8529232</v>
       </c>
       <c r="O57">
-        <v>2.345466779999999</v>
+        <v>2.313526175999999</v>
       </c>
       <c r="P57">
-        <v>10.68490422</v>
+        <v>10.539397024</v>
       </c>
       <c r="Q57">
-        <v>15.89490422</v>
+        <v>15.749397024</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1436503262857393</v>
+        <v>0.1456742710832952</v>
       </c>
       <c r="T57">
-        <v>1.649897075070744</v>
+        <v>1.684023692000368</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.335129747247564</v>
+        <v>2.293431001761</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0989040392766499</v>
+        <v>0.0989796317247171</v>
       </c>
       <c r="C58">
-        <v>93.07833505982578</v>
+        <v>90.53143006631893</v>
       </c>
       <c r="D58">
-        <v>220.5343350598258</v>
+        <v>220.328430066319</v>
       </c>
       <c r="E58">
-        <v>61.89600000000003</v>
+        <v>64.23700000000004</v>
       </c>
       <c r="F58">
-        <v>131.096</v>
+        <v>133.437</v>
       </c>
       <c r="G58">
         <v>3.64</v>
@@ -6043,28 +6043,28 @@
         <v>22.79</v>
       </c>
       <c r="M58">
-        <v>9.937076800000003</v>
+        <v>10.1145246</v>
       </c>
       <c r="N58">
-        <v>12.8529232</v>
+        <v>12.67547539999999</v>
       </c>
       <c r="O58">
-        <v>2.313526175999999</v>
+        <v>2.281585571999999</v>
       </c>
       <c r="P58">
-        <v>10.539397024</v>
+        <v>10.393889828</v>
       </c>
       <c r="Q58">
-        <v>15.749397024</v>
+        <v>15.603889828</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1456742710832952</v>
+        <v>0.1477923528481793</v>
       </c>
       <c r="T58">
-        <v>1.684023692000368</v>
+        <v>1.719737593438347</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.293431001761</v>
+        <v>2.253195370151158</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0989796317247171</v>
+        <v>0.09905522417278431</v>
       </c>
       <c r="C59">
-        <v>90.53143006631893</v>
+        <v>87.98490920636507</v>
       </c>
       <c r="D59">
-        <v>220.328430066319</v>
+        <v>220.1229092063651</v>
       </c>
       <c r="E59">
-        <v>64.23700000000004</v>
+        <v>66.57800000000002</v>
       </c>
       <c r="F59">
-        <v>133.437</v>
+        <v>135.778</v>
       </c>
       <c r="G59">
         <v>3.64</v>
@@ -6125,28 +6125,28 @@
         <v>22.79</v>
       </c>
       <c r="M59">
-        <v>10.1145246</v>
+        <v>10.2919724</v>
       </c>
       <c r="N59">
-        <v>12.67547539999999</v>
+        <v>12.4980276</v>
       </c>
       <c r="O59">
-        <v>2.281585571999999</v>
+        <v>2.249644967999999</v>
       </c>
       <c r="P59">
-        <v>10.393889828</v>
+        <v>10.248382632</v>
       </c>
       <c r="Q59">
-        <v>15.603889828</v>
+        <v>15.458382632</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1477923528481793</v>
+        <v>0.1500112956494865</v>
       </c>
       <c r="T59">
-        <v>1.719737593438347</v>
+        <v>1.757152156849562</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.253195370151158</v>
+        <v>2.214347174114069</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09905522417278431</v>
+        <v>0.09913081662085151</v>
       </c>
       <c r="C60">
-        <v>87.9849092063651</v>
+        <v>85.43877140601461</v>
       </c>
       <c r="D60">
-        <v>220.1229092063651</v>
+        <v>219.9177714060146</v>
       </c>
       <c r="E60">
-        <v>66.57799999999999</v>
+        <v>68.919</v>
       </c>
       <c r="F60">
-        <v>135.778</v>
+        <v>138.119</v>
       </c>
       <c r="G60">
         <v>3.64</v>
@@ -6207,28 +6207,28 @@
         <v>22.79</v>
       </c>
       <c r="M60">
-        <v>10.2919724</v>
+        <v>10.4694202</v>
       </c>
       <c r="N60">
-        <v>12.4980276</v>
+        <v>12.3205798</v>
       </c>
       <c r="O60">
-        <v>2.249644968</v>
+        <v>2.217704364</v>
       </c>
       <c r="P60">
-        <v>10.248382632</v>
+        <v>10.102875436</v>
       </c>
       <c r="Q60">
-        <v>15.458382632</v>
+        <v>15.312875436</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1500112956494865</v>
+        <v>0.1523384795630524</v>
       </c>
       <c r="T60">
-        <v>1.757152156849562</v>
+        <v>1.796391820914983</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.214347174114069</v>
+        <v>2.176815866078238</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09913081662085151</v>
+        <v>0.09920640906891873</v>
       </c>
       <c r="C61">
-        <v>85.43877140601461</v>
+        <v>82.89301559531719</v>
       </c>
       <c r="D61">
-        <v>219.9177714060146</v>
+        <v>219.7130155953172</v>
       </c>
       <c r="E61">
-        <v>68.919</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="F61">
-        <v>138.119</v>
+        <v>140.46</v>
       </c>
       <c r="G61">
         <v>3.64</v>
@@ -6289,28 +6289,28 @@
         <v>22.79</v>
       </c>
       <c r="M61">
-        <v>10.4694202</v>
+        <v>10.646868</v>
       </c>
       <c r="N61">
-        <v>12.3205798</v>
+        <v>12.143132</v>
       </c>
       <c r="O61">
-        <v>2.217704364</v>
+        <v>2.18576376</v>
       </c>
       <c r="P61">
-        <v>10.102875436</v>
+        <v>9.957368239999997</v>
       </c>
       <c r="Q61">
-        <v>15.312875436</v>
+        <v>15.16736824</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1523384795630524</v>
+        <v>0.1547820226722968</v>
       </c>
       <c r="T61">
-        <v>1.796391820914983</v>
+        <v>1.837593468183676</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.176815866078238</v>
+        <v>2.140535601643601</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09920640906891873</v>
+        <v>0.09928200151698593</v>
       </c>
       <c r="C62">
-        <v>82.89301559531719</v>
+        <v>80.34764070830394</v>
       </c>
       <c r="D62">
-        <v>219.7130155953172</v>
+        <v>219.508640708304</v>
       </c>
       <c r="E62">
-        <v>71.26000000000001</v>
+        <v>73.60100000000001</v>
       </c>
       <c r="F62">
-        <v>140.46</v>
+        <v>142.801</v>
       </c>
       <c r="G62">
         <v>3.64</v>
@@ -6371,28 +6371,28 @@
         <v>22.79</v>
       </c>
       <c r="M62">
-        <v>10.646868</v>
+        <v>10.8243158</v>
       </c>
       <c r="N62">
-        <v>12.143132</v>
+        <v>11.9656842</v>
       </c>
       <c r="O62">
-        <v>2.18576376</v>
+        <v>2.153823155999999</v>
       </c>
       <c r="P62">
-        <v>9.957368239999997</v>
+        <v>9.811861043999997</v>
       </c>
       <c r="Q62">
-        <v>15.16736824</v>
+        <v>15.021861044</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1547820226722968</v>
+        <v>0.1573508756845793</v>
       </c>
       <c r="T62">
-        <v>1.837593468183676</v>
+        <v>1.880908020440506</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.140535601643601</v>
+        <v>2.105444854075672</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09928200151698593</v>
+        <v>0.09935759396505311</v>
       </c>
       <c r="C63">
-        <v>80.34764070830394</v>
+        <v>77.8026456829684</v>
       </c>
       <c r="D63">
-        <v>219.508640708304</v>
+        <v>219.3046456829684</v>
       </c>
       <c r="E63">
-        <v>73.60100000000001</v>
+        <v>75.94200000000002</v>
       </c>
       <c r="F63">
-        <v>142.801</v>
+        <v>145.142</v>
       </c>
       <c r="G63">
         <v>3.64</v>
@@ -6453,28 +6453,28 @@
         <v>22.79</v>
       </c>
       <c r="M63">
-        <v>10.8243158</v>
+        <v>11.0017636</v>
       </c>
       <c r="N63">
-        <v>11.9656842</v>
+        <v>11.7882364</v>
       </c>
       <c r="O63">
-        <v>2.153823155999999</v>
+        <v>2.121882551999999</v>
       </c>
       <c r="P63">
-        <v>9.811861043999997</v>
+        <v>9.666353847999998</v>
       </c>
       <c r="Q63">
-        <v>15.021861044</v>
+        <v>14.876353848</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1573508756845793</v>
+        <v>0.1600549314869819</v>
       </c>
       <c r="T63">
-        <v>1.880908020440506</v>
+        <v>1.926502285974012</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.105444854075672</v>
+        <v>2.07148606610671</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09935759396505311</v>
+        <v>0.09943318641312032</v>
       </c>
       <c r="C64">
-        <v>77.8026456829684</v>
+        <v>75.25802946124801</v>
       </c>
       <c r="D64">
-        <v>219.3046456829684</v>
+        <v>219.101029461248</v>
       </c>
       <c r="E64">
-        <v>75.94200000000002</v>
+        <v>78.283</v>
       </c>
       <c r="F64">
-        <v>145.142</v>
+        <v>147.483</v>
       </c>
       <c r="G64">
         <v>3.64</v>
@@ -6535,28 +6535,28 @@
         <v>22.79</v>
       </c>
       <c r="M64">
-        <v>11.0017636</v>
+        <v>11.1792114</v>
       </c>
       <c r="N64">
-        <v>11.7882364</v>
+        <v>11.6107886</v>
       </c>
       <c r="O64">
-        <v>2.121882551999999</v>
+        <v>2.089941947999999</v>
       </c>
       <c r="P64">
-        <v>9.666353847999998</v>
+        <v>9.520846651999998</v>
       </c>
       <c r="Q64">
-        <v>14.876353848</v>
+        <v>14.730846652</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1600549314869819</v>
+        <v>0.1629051524678928</v>
       </c>
       <c r="T64">
-        <v>1.926502285974012</v>
+        <v>1.974561106401221</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.07148606610671</v>
+        <v>2.038605334898667</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09943318641312032</v>
+        <v>0.09950877886118753</v>
       </c>
       <c r="C65">
-        <v>75.25802946124801</v>
+        <v>72.71379098900624</v>
       </c>
       <c r="D65">
-        <v>219.101029461248</v>
+        <v>218.8977909890063</v>
       </c>
       <c r="E65">
-        <v>78.283</v>
+        <v>80.62400000000001</v>
       </c>
       <c r="F65">
-        <v>147.483</v>
+        <v>149.824</v>
       </c>
       <c r="G65">
         <v>3.64</v>
@@ -6617,28 +6617,28 @@
         <v>22.79</v>
       </c>
       <c r="M65">
-        <v>11.1792114</v>
+        <v>11.3566592</v>
       </c>
       <c r="N65">
-        <v>11.6107886</v>
+        <v>11.4333408</v>
       </c>
       <c r="O65">
-        <v>2.089941947999999</v>
+        <v>2.058001344</v>
       </c>
       <c r="P65">
-        <v>9.520846651999998</v>
+        <v>9.375339455999999</v>
       </c>
       <c r="Q65">
-        <v>14.730846652</v>
+        <v>14.585339456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1629051524678928</v>
+        <v>0.1659137190588543</v>
       </c>
       <c r="T65">
-        <v>1.974561106401221</v>
+        <v>2.025289861296608</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.038605334898667</v>
+        <v>2.006752126540875</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09950877886118753</v>
+        <v>0.1071529713092547</v>
       </c>
       <c r="C66">
-        <v>72.71379098900624</v>
+        <v>51.60050561678312</v>
       </c>
       <c r="D66">
-        <v>218.8977909890063</v>
+        <v>200.1255056167832</v>
       </c>
       <c r="E66">
-        <v>80.62400000000001</v>
+        <v>82.96500000000002</v>
       </c>
       <c r="F66">
-        <v>149.824</v>
+        <v>152.165</v>
       </c>
       <c r="G66">
         <v>3.64</v>
@@ -6699,45 +6699,45 @@
         <v>22.79</v>
       </c>
       <c r="M66">
-        <v>11.3566592</v>
+        <v>13.69485</v>
       </c>
       <c r="N66">
-        <v>11.4333408</v>
+        <v>9.095149999999999</v>
       </c>
       <c r="O66">
-        <v>2.058001344</v>
+        <v>1.637127</v>
       </c>
       <c r="P66">
-        <v>9.375339455999999</v>
+        <v>7.458022999999999</v>
       </c>
       <c r="Q66">
-        <v>14.585339456</v>
+        <v>12.668023</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1659137190588543</v>
+        <v>0.1690942037407278</v>
       </c>
       <c r="T66">
-        <v>2.025289861296608</v>
+        <v>2.078917402186017</v>
       </c>
       <c r="U66">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
         <v>0.18</v>
       </c>
       <c r="W66">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.006752126540875</v>
+        <v>1.664129216457281</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1071529713092547</v>
+        <v>0.1073450037573219</v>
       </c>
       <c r="C67">
-        <v>51.60050561678312</v>
+        <v>48.82928957936952</v>
       </c>
       <c r="D67">
-        <v>200.1255056167832</v>
+        <v>199.6952895793696</v>
       </c>
       <c r="E67">
-        <v>82.96500000000002</v>
+        <v>85.30600000000003</v>
       </c>
       <c r="F67">
-        <v>152.165</v>
+        <v>154.506</v>
       </c>
       <c r="G67">
         <v>3.64</v>
@@ -6781,28 +6781,28 @@
         <v>22.79</v>
       </c>
       <c r="M67">
-        <v>13.69485</v>
+        <v>13.90554</v>
       </c>
       <c r="N67">
-        <v>9.095149999999999</v>
+        <v>8.884459999999997</v>
       </c>
       <c r="O67">
-        <v>1.637127</v>
+        <v>1.599202799999999</v>
       </c>
       <c r="P67">
-        <v>7.458022999999999</v>
+        <v>7.285257199999998</v>
       </c>
       <c r="Q67">
-        <v>12.668023</v>
+        <v>12.4952572</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1690942037407278</v>
+        <v>0.1724617757568292</v>
       </c>
       <c r="T67">
-        <v>2.078917402186017</v>
+        <v>2.135699504304214</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.664129216457281</v>
+        <v>1.638915137420049</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1073450037573219</v>
+        <v>0.1075370362053892</v>
       </c>
       <c r="C68">
-        <v>48.82928957936952</v>
+        <v>46.05991927178422</v>
       </c>
       <c r="D68">
-        <v>199.6952895793696</v>
+        <v>199.2669192717843</v>
       </c>
       <c r="E68">
-        <v>85.30600000000003</v>
+        <v>87.64700000000003</v>
       </c>
       <c r="F68">
-        <v>154.506</v>
+        <v>156.847</v>
       </c>
       <c r="G68">
         <v>3.64</v>
@@ -6863,28 +6863,28 @@
         <v>22.79</v>
       </c>
       <c r="M68">
-        <v>13.90554</v>
+        <v>14.11623</v>
       </c>
       <c r="N68">
-        <v>8.884459999999997</v>
+        <v>8.673769999999996</v>
       </c>
       <c r="O68">
-        <v>1.599202799999999</v>
+        <v>1.561278599999999</v>
       </c>
       <c r="P68">
-        <v>7.285257199999998</v>
+        <v>7.112491399999996</v>
       </c>
       <c r="Q68">
-        <v>12.4952572</v>
+        <v>12.3224914</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1724617757568292</v>
+        <v>0.1760334430466338</v>
       </c>
       <c r="T68">
-        <v>2.135699504304214</v>
+        <v>2.195922945944727</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.638915137420049</v>
+        <v>1.614453717458556</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1075370362053892</v>
+        <v>0.1077290686534564</v>
       </c>
       <c r="C69">
-        <v>46.05991927178422</v>
+        <v>43.29238284151785</v>
       </c>
       <c r="D69">
-        <v>199.2669192717843</v>
+        <v>198.8403828415179</v>
       </c>
       <c r="E69">
-        <v>87.64700000000003</v>
+        <v>89.98800000000001</v>
       </c>
       <c r="F69">
-        <v>156.847</v>
+        <v>159.188</v>
       </c>
       <c r="G69">
         <v>3.64</v>
@@ -6945,28 +6945,28 @@
         <v>22.79</v>
       </c>
       <c r="M69">
-        <v>14.11623</v>
+        <v>14.32692</v>
       </c>
       <c r="N69">
-        <v>8.673769999999996</v>
+        <v>8.463079999999998</v>
       </c>
       <c r="O69">
-        <v>1.561278599999999</v>
+        <v>1.5233544</v>
       </c>
       <c r="P69">
-        <v>7.112491399999996</v>
+        <v>6.939725599999998</v>
       </c>
       <c r="Q69">
-        <v>12.3224914</v>
+        <v>12.1497256</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1760334430466338</v>
+        <v>0.1798283395420511</v>
       </c>
       <c r="T69">
-        <v>2.195922945944727</v>
+        <v>2.259910352687772</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.614453717458556</v>
+        <v>1.590711751025342</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1077290686534564</v>
+        <v>0.1079211011015236</v>
       </c>
       <c r="C70">
-        <v>43.29238284151785</v>
+        <v>40.52666853732671</v>
       </c>
       <c r="D70">
-        <v>198.8403828415179</v>
+        <v>198.4156685373268</v>
       </c>
       <c r="E70">
-        <v>89.98800000000001</v>
+        <v>92.32900000000002</v>
       </c>
       <c r="F70">
-        <v>159.188</v>
+        <v>161.529</v>
       </c>
       <c r="G70">
         <v>3.64</v>
@@ -7027,28 +7027,28 @@
         <v>22.79</v>
       </c>
       <c r="M70">
-        <v>14.32692</v>
+        <v>14.53761</v>
       </c>
       <c r="N70">
-        <v>8.463079999999998</v>
+        <v>8.252389999999998</v>
       </c>
       <c r="O70">
-        <v>1.5233544</v>
+        <v>1.4854302</v>
       </c>
       <c r="P70">
-        <v>6.939725599999998</v>
+        <v>6.766959799999999</v>
       </c>
       <c r="Q70">
-        <v>12.1497256</v>
+        <v>11.9769598</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1798283395420511</v>
+        <v>0.1838680680694309</v>
       </c>
       <c r="T70">
-        <v>2.259910352687772</v>
+        <v>2.328025979220691</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.590711751025342</v>
+        <v>1.567657957532222</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1079211011015236</v>
+        <v>0.1081131335495908</v>
       </c>
       <c r="C71">
-        <v>40.52666853732671</v>
+        <v>37.76276470815364</v>
       </c>
       <c r="D71">
-        <v>198.4156685373268</v>
+        <v>197.9927647081537</v>
       </c>
       <c r="E71">
-        <v>92.32900000000002</v>
+        <v>94.67000000000003</v>
       </c>
       <c r="F71">
-        <v>161.529</v>
+        <v>163.87</v>
       </c>
       <c r="G71">
         <v>3.64</v>
@@ -7109,28 +7109,28 @@
         <v>22.79</v>
       </c>
       <c r="M71">
-        <v>14.53761</v>
+        <v>14.7483</v>
       </c>
       <c r="N71">
-        <v>8.252389999999998</v>
+        <v>8.041699999999997</v>
       </c>
       <c r="O71">
-        <v>1.4854302</v>
+        <v>1.447505999999999</v>
       </c>
       <c r="P71">
-        <v>6.766959799999999</v>
+        <v>6.594193999999998</v>
       </c>
       <c r="Q71">
-        <v>11.9769598</v>
+        <v>11.804194</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1838680680694309</v>
+        <v>0.1881771118319693</v>
       </c>
       <c r="T71">
-        <v>2.328025979220691</v>
+        <v>2.400682647522471</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.567657957532222</v>
+        <v>1.54526284385319</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1081131335495908</v>
+        <v>0.108305165997658</v>
       </c>
       <c r="C72">
-        <v>37.76276470815364</v>
+        <v>35.00065980206284</v>
       </c>
       <c r="D72">
-        <v>197.9927647081537</v>
+        <v>197.5716598020629</v>
       </c>
       <c r="E72">
-        <v>94.67000000000003</v>
+        <v>97.01100000000004</v>
       </c>
       <c r="F72">
-        <v>163.87</v>
+        <v>166.211</v>
       </c>
       <c r="G72">
         <v>3.64</v>
@@ -7191,28 +7191,28 @@
         <v>22.79</v>
       </c>
       <c r="M72">
-        <v>14.7483</v>
+        <v>14.95899</v>
       </c>
       <c r="N72">
-        <v>8.041699999999997</v>
+        <v>7.831009999999996</v>
       </c>
       <c r="O72">
-        <v>1.447505999999999</v>
+        <v>1.409581799999999</v>
       </c>
       <c r="P72">
-        <v>6.594193999999998</v>
+        <v>6.421428199999997</v>
       </c>
       <c r="Q72">
-        <v>11.804194</v>
+        <v>11.6314282</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1881771118319693</v>
+        <v>0.1927833310264068</v>
       </c>
       <c r="T72">
-        <v>2.400682647522471</v>
+        <v>2.478350120534718</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.54526284385319</v>
+        <v>1.523498578446806</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.108305165997658</v>
+        <v>0.1084971984457252</v>
       </c>
       <c r="C73">
-        <v>35.00065980206284</v>
+        <v>32.24034236518756</v>
       </c>
       <c r="D73">
-        <v>197.5716598020629</v>
+        <v>197.1523423651876</v>
       </c>
       <c r="E73">
-        <v>97.01100000000001</v>
+        <v>99.35200000000002</v>
       </c>
       <c r="F73">
-        <v>166.211</v>
+        <v>168.552</v>
       </c>
       <c r="G73">
         <v>3.64</v>
@@ -7273,28 +7273,28 @@
         <v>22.79</v>
       </c>
       <c r="M73">
-        <v>14.95899</v>
+        <v>15.16968</v>
       </c>
       <c r="N73">
-        <v>7.831009999999999</v>
+        <v>7.620319999999998</v>
       </c>
       <c r="O73">
-        <v>1.4095818</v>
+        <v>1.3716576</v>
       </c>
       <c r="P73">
-        <v>6.421428199999999</v>
+        <v>6.248662399999998</v>
       </c>
       <c r="Q73">
-        <v>11.6314282</v>
+        <v>11.4586624</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1927833310264068</v>
+        <v>0.1977185658775899</v>
       </c>
       <c r="T73">
-        <v>2.478350120534718</v>
+        <v>2.561565270190697</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.523498578446807</v>
+        <v>1.502338875968379</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1084971984457252</v>
+        <v>0.1450439450666622</v>
       </c>
       <c r="C74">
-        <v>32.24034236518756</v>
+        <v>-26.82282481474562</v>
       </c>
       <c r="D74">
-        <v>197.1523423651876</v>
+        <v>140.4301751852544</v>
       </c>
       <c r="E74">
-        <v>99.35200000000002</v>
+        <v>101.693</v>
       </c>
       <c r="F74">
-        <v>168.552</v>
+        <v>170.893</v>
       </c>
       <c r="G74">
         <v>3.64</v>
@@ -7355,45 +7355,45 @@
         <v>22.79</v>
       </c>
       <c r="M74">
-        <v>15.16968</v>
+        <v>25.0870924</v>
       </c>
       <c r="N74">
-        <v>7.620319999999998</v>
+        <v>-2.297092400000004</v>
       </c>
       <c r="O74">
-        <v>1.3716576</v>
+        <v>-0.4134766320000007</v>
       </c>
       <c r="P74">
-        <v>6.248662399999998</v>
+        <v>-1.883615768000003</v>
       </c>
       <c r="Q74">
-        <v>11.4586624</v>
+        <v>3.326384231999997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1977185658775899</v>
+        <v>0.2051971322813235</v>
       </c>
       <c r="T74">
-        <v>2.561565270190697</v>
+        <v>2.687664643627746</v>
       </c>
       <c r="U74">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.18</v>
+        <v>0.1635183517720052</v>
       </c>
       <c r="W74">
-        <v>0.0738</v>
+        <v>0.1227955059598696</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.502338875968379</v>
+        <v>0.9084352876222513</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1450439450666622</v>
+        <v>0.1460539450666622</v>
       </c>
       <c r="C75">
-        <v>-26.82282481474562</v>
+        <v>-30.27158188186252</v>
       </c>
       <c r="D75">
-        <v>140.4301751852544</v>
+        <v>139.3224181181375</v>
       </c>
       <c r="E75">
-        <v>101.693</v>
+        <v>104.034</v>
       </c>
       <c r="F75">
-        <v>170.893</v>
+        <v>173.234</v>
       </c>
       <c r="G75">
         <v>3.64</v>
@@ -7437,37 +7437,37 @@
         <v>22.79</v>
       </c>
       <c r="M75">
-        <v>25.0870924</v>
+        <v>25.4307512</v>
       </c>
       <c r="N75">
-        <v>-2.297092400000004</v>
+        <v>-2.640751200000004</v>
       </c>
       <c r="O75">
-        <v>-0.4134766320000007</v>
+        <v>-0.4753352160000007</v>
       </c>
       <c r="P75">
-        <v>-1.883615768000003</v>
+        <v>-2.165415984000003</v>
       </c>
       <c r="Q75">
-        <v>3.326384231999997</v>
+        <v>3.044584015999997</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2051971322813235</v>
+        <v>0.2113277912152206</v>
       </c>
       <c r="T75">
-        <v>2.687664643627746</v>
+        <v>2.791036360690351</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1635183517720052</v>
+        <v>0.1613086443156268</v>
       </c>
       <c r="W75">
-        <v>0.1227955059598696</v>
+        <v>0.123119891014466</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9084352876222513</v>
+        <v>0.8961591350868156</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1460539450666622</v>
+        <v>0.1470639450666622</v>
       </c>
       <c r="C76">
-        <v>-30.27158188186252</v>
+        <v>-33.70299906418364</v>
       </c>
       <c r="D76">
-        <v>139.3224181181375</v>
+        <v>138.2320009358164</v>
       </c>
       <c r="E76">
-        <v>104.034</v>
+        <v>106.375</v>
       </c>
       <c r="F76">
-        <v>173.234</v>
+        <v>175.575</v>
       </c>
       <c r="G76">
         <v>3.64</v>
@@ -7519,37 +7519,37 @@
         <v>22.79</v>
       </c>
       <c r="M76">
-        <v>25.4307512</v>
+        <v>25.77441000000001</v>
       </c>
       <c r="N76">
-        <v>-2.640751200000004</v>
+        <v>-2.984410000000008</v>
       </c>
       <c r="O76">
-        <v>-0.4753352160000007</v>
+        <v>-0.5371938000000014</v>
       </c>
       <c r="P76">
-        <v>-2.165415984000003</v>
+        <v>-2.447216200000006</v>
       </c>
       <c r="Q76">
-        <v>3.044584015999997</v>
+        <v>2.762783799999994</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2113277912152206</v>
+        <v>0.2179489028638294</v>
       </c>
       <c r="T76">
-        <v>2.791036360690351</v>
+        <v>2.902677815117965</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1613086443156268</v>
+        <v>0.1591578623914184</v>
       </c>
       <c r="W76">
-        <v>0.123119891014466</v>
+        <v>0.1234356258009398</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8961591350868156</v>
+        <v>0.8842103466189912</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1470639450666622</v>
+        <v>0.1480739450666622</v>
       </c>
       <c r="C77">
-        <v>-33.70299906418364</v>
+        <v>-37.11748033563933</v>
       </c>
       <c r="D77">
-        <v>138.2320009358164</v>
+        <v>137.1585196643607</v>
       </c>
       <c r="E77">
-        <v>106.375</v>
+        <v>108.716</v>
       </c>
       <c r="F77">
-        <v>175.575</v>
+        <v>177.916</v>
       </c>
       <c r="G77">
         <v>3.64</v>
@@ -7601,37 +7601,37 @@
         <v>22.79</v>
       </c>
       <c r="M77">
-        <v>25.77441000000001</v>
+        <v>26.11806880000001</v>
       </c>
       <c r="N77">
-        <v>-2.984410000000008</v>
+        <v>-3.328068800000008</v>
       </c>
       <c r="O77">
-        <v>-0.5371938000000014</v>
+        <v>-0.5990523840000014</v>
       </c>
       <c r="P77">
-        <v>-2.447216200000006</v>
+        <v>-2.729016416000006</v>
       </c>
       <c r="Q77">
-        <v>2.762783799999994</v>
+        <v>2.480983583999994</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2179489028638294</v>
+        <v>0.225121773816489</v>
       </c>
       <c r="T77">
-        <v>2.902677815117965</v>
+        <v>3.023622724081214</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1591578623914184</v>
+        <v>0.1570636799915313</v>
       </c>
       <c r="W77">
-        <v>0.1234356258009398</v>
+        <v>0.1237430517772432</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8842103466189912</v>
+        <v>0.8725759999529519</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1480739450666622</v>
+        <v>0.1490839450666622</v>
       </c>
       <c r="C78">
-        <v>-37.11748033563933</v>
+        <v>-40.5154172181463</v>
       </c>
       <c r="D78">
-        <v>137.1585196643607</v>
+        <v>136.1015827818538</v>
       </c>
       <c r="E78">
-        <v>108.716</v>
+        <v>111.057</v>
       </c>
       <c r="F78">
-        <v>177.916</v>
+        <v>180.257</v>
       </c>
       <c r="G78">
         <v>3.64</v>
@@ -7683,37 +7683,37 @@
         <v>22.79</v>
       </c>
       <c r="M78">
-        <v>26.11806880000001</v>
+        <v>26.46172760000001</v>
       </c>
       <c r="N78">
-        <v>-3.328068800000008</v>
+        <v>-3.671727600000008</v>
       </c>
       <c r="O78">
-        <v>-0.5990523840000014</v>
+        <v>-0.6609109680000014</v>
       </c>
       <c r="P78">
-        <v>-2.729016416000006</v>
+        <v>-3.010816632000006</v>
       </c>
       <c r="Q78">
-        <v>2.480983583999994</v>
+        <v>2.199183367999994</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.225121773816489</v>
+        <v>0.2329183726780754</v>
       </c>
       <c r="T78">
-        <v>3.023622724081214</v>
+        <v>3.155084581649962</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1570636799915313</v>
+        <v>0.1550238919396933</v>
       </c>
       <c r="W78">
-        <v>0.1237430517772432</v>
+        <v>0.124042492663253</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8725759999529519</v>
+        <v>0.861243844109407</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1490839450666622</v>
+        <v>0.1500939450666622</v>
       </c>
       <c r="C79">
-        <v>-40.5154172181463</v>
+        <v>-43.89718925771146</v>
       </c>
       <c r="D79">
-        <v>136.1015827818538</v>
+        <v>135.0608107422886</v>
       </c>
       <c r="E79">
-        <v>111.057</v>
+        <v>113.398</v>
       </c>
       <c r="F79">
-        <v>180.257</v>
+        <v>182.598</v>
       </c>
       <c r="G79">
         <v>3.64</v>
@@ -7765,37 +7765,37 @@
         <v>22.79</v>
       </c>
       <c r="M79">
-        <v>26.46172760000001</v>
+        <v>26.8053864</v>
       </c>
       <c r="N79">
-        <v>-3.671727600000008</v>
+        <v>-4.015386400000004</v>
       </c>
       <c r="O79">
-        <v>-0.6609109680000014</v>
+        <v>-0.7227695520000007</v>
       </c>
       <c r="P79">
-        <v>-3.010816632000006</v>
+        <v>-3.292616848000003</v>
       </c>
       <c r="Q79">
-        <v>2.199183367999994</v>
+        <v>1.917383151999997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2329183726780754</v>
+        <v>0.2414237532543516</v>
       </c>
       <c r="T79">
-        <v>3.155084581649962</v>
+        <v>3.298497517179506</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1550238919396933</v>
+        <v>0.1530364061455946</v>
       </c>
       <c r="W79">
-        <v>0.124042492663253</v>
+        <v>0.1243342555778267</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.861243844109407</v>
+        <v>0.8502022563644147</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1500939450666622</v>
+        <v>0.1511039450666622</v>
       </c>
       <c r="C80">
-        <v>-43.89718925771146</v>
+        <v>-47.26316447885753</v>
       </c>
       <c r="D80">
-        <v>135.0608107422886</v>
+        <v>134.0358355211425</v>
       </c>
       <c r="E80">
-        <v>113.398</v>
+        <v>115.739</v>
       </c>
       <c r="F80">
-        <v>182.598</v>
+        <v>184.939</v>
       </c>
       <c r="G80">
         <v>3.64</v>
@@ -7847,37 +7847,37 @@
         <v>22.79</v>
       </c>
       <c r="M80">
-        <v>26.8053864</v>
+        <v>27.14904520000001</v>
       </c>
       <c r="N80">
-        <v>-4.015386400000004</v>
+        <v>-4.359045200000008</v>
       </c>
       <c r="O80">
-        <v>-0.7227695520000007</v>
+        <v>-0.7846281360000014</v>
       </c>
       <c r="P80">
-        <v>-3.292616848000003</v>
+        <v>-3.574417064000007</v>
       </c>
       <c r="Q80">
-        <v>1.917383151999997</v>
+        <v>1.635582935999993</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2414237532543516</v>
+        <v>0.2507391700759874</v>
       </c>
       <c r="T80">
-        <v>3.298497517179506</v>
+        <v>3.455568827521388</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1530364061455946</v>
+        <v>0.1510992364475491</v>
       </c>
       <c r="W80">
-        <v>0.1243342555778267</v>
+        <v>0.1246186320894998</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8502022563644147</v>
+        <v>0.8394402024863841</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1511039450666622</v>
+        <v>0.1521139450666622</v>
       </c>
       <c r="C81">
-        <v>-47.26316447885753</v>
+        <v>-50.61369981851232</v>
       </c>
       <c r="D81">
-        <v>134.0358355211425</v>
+        <v>133.0263001814877</v>
       </c>
       <c r="E81">
-        <v>115.739</v>
+        <v>118.08</v>
       </c>
       <c r="F81">
-        <v>184.939</v>
+        <v>187.28</v>
       </c>
       <c r="G81">
         <v>3.64</v>
@@ -7929,37 +7929,37 @@
         <v>22.79</v>
       </c>
       <c r="M81">
-        <v>27.14904520000001</v>
+        <v>27.49270400000001</v>
       </c>
       <c r="N81">
-        <v>-4.359045200000008</v>
+        <v>-4.702704000000008</v>
       </c>
       <c r="O81">
-        <v>-0.7846281360000014</v>
+        <v>-0.8464867200000014</v>
       </c>
       <c r="P81">
-        <v>-3.574417064000007</v>
+        <v>-3.856217280000006</v>
       </c>
       <c r="Q81">
-        <v>1.635582935999993</v>
+        <v>1.353782719999994</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2507391700759874</v>
+        <v>0.2609861285797868</v>
       </c>
       <c r="T81">
-        <v>3.455568827521388</v>
+        <v>3.628347268897457</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1510992364475491</v>
+        <v>0.1492104959919548</v>
       </c>
       <c r="W81">
-        <v>0.1246186320894998</v>
+        <v>0.1248958991883811</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8394402024863841</v>
+        <v>0.8289471999553043</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1521139450666622</v>
+        <v>0.1531239450666622</v>
       </c>
       <c r="C82">
-        <v>-50.61369981851232</v>
+        <v>-53.94914154043681</v>
       </c>
       <c r="D82">
-        <v>133.0263001814877</v>
+        <v>132.0318584595632</v>
       </c>
       <c r="E82">
-        <v>118.08</v>
+        <v>120.421</v>
       </c>
       <c r="F82">
-        <v>187.28</v>
+        <v>189.621</v>
       </c>
       <c r="G82">
         <v>3.64</v>
@@ -8011,37 +8011,37 @@
         <v>22.79</v>
       </c>
       <c r="M82">
-        <v>27.49270400000001</v>
+        <v>27.83636280000001</v>
       </c>
       <c r="N82">
-        <v>-4.702704000000008</v>
+        <v>-5.046362800000008</v>
       </c>
       <c r="O82">
-        <v>-0.8464867200000014</v>
+        <v>-0.9083453040000014</v>
       </c>
       <c r="P82">
-        <v>-3.856217280000006</v>
+        <v>-4.138017496000007</v>
       </c>
       <c r="Q82">
-        <v>1.353782719999994</v>
+        <v>1.071982503999993</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2609861285797868</v>
+        <v>0.2723117142945125</v>
       </c>
       <c r="T82">
-        <v>3.628347268897457</v>
+        <v>3.819312914628903</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1492104959919548</v>
+        <v>0.1473683911031652</v>
       </c>
       <c r="W82">
-        <v>0.1248958991883811</v>
+        <v>0.1251663201860554</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8289471999553043</v>
+        <v>0.8187132839064734</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1531239450666622</v>
+        <v>0.1541339450666622</v>
       </c>
       <c r="C83">
-        <v>-53.94914154043681</v>
+        <v>-57.26982563120262</v>
       </c>
       <c r="D83">
-        <v>132.0318584595632</v>
+        <v>131.0521743687974</v>
       </c>
       <c r="E83">
-        <v>120.421</v>
+        <v>122.762</v>
       </c>
       <c r="F83">
-        <v>189.621</v>
+        <v>191.962</v>
       </c>
       <c r="G83">
         <v>3.64</v>
@@ -8093,37 +8093,37 @@
         <v>22.79</v>
       </c>
       <c r="M83">
-        <v>27.83636280000001</v>
+        <v>28.18002160000001</v>
       </c>
       <c r="N83">
-        <v>-5.046362800000008</v>
+        <v>-5.390021600000011</v>
       </c>
       <c r="O83">
-        <v>-0.9083453040000014</v>
+        <v>-0.970203888000002</v>
       </c>
       <c r="P83">
-        <v>-4.138017496000007</v>
+        <v>-4.419817712000009</v>
       </c>
       <c r="Q83">
-        <v>1.071982503999993</v>
+        <v>0.7901822879999907</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2723117142945125</v>
+        <v>0.2848956984219854</v>
       </c>
       <c r="T83">
-        <v>3.819312914628903</v>
+        <v>4.03149696544162</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1473683911031652</v>
+        <v>0.1455712156019071</v>
       </c>
       <c r="W83">
-        <v>0.1251663201860554</v>
+        <v>0.12543014554964</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8187132839064734</v>
+        <v>0.8087289755661504</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1541339450666622</v>
+        <v>0.2015327516867925</v>
       </c>
       <c r="C84">
-        <v>-57.26982563120262</v>
+        <v>-93.45912948655378</v>
       </c>
       <c r="D84">
-        <v>131.0521743687974</v>
+        <v>97.20387051344625</v>
       </c>
       <c r="E84">
-        <v>122.762</v>
+        <v>125.103</v>
       </c>
       <c r="F84">
-        <v>191.962</v>
+        <v>194.303</v>
       </c>
       <c r="G84">
         <v>3.64</v>
@@ -8175,45 +8175,45 @@
         <v>22.79</v>
       </c>
       <c r="M84">
-        <v>28.18002160000001</v>
+        <v>39.0160424</v>
       </c>
       <c r="N84">
-        <v>-5.390021600000011</v>
+        <v>-16.2260424</v>
       </c>
       <c r="O84">
-        <v>-0.970203888000002</v>
+        <v>-2.920687632000001</v>
       </c>
       <c r="P84">
-        <v>-4.419817712000009</v>
+        <v>-13.305354768</v>
       </c>
       <c r="Q84">
-        <v>0.7901822879999907</v>
+        <v>-8.095354768000004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2848956984219854</v>
+        <v>0.3081884255063983</v>
       </c>
       <c r="T84">
-        <v>4.03149696544162</v>
+        <v>4.424245806919881</v>
       </c>
       <c r="U84">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1455712156019071</v>
+        <v>0.1051413661576295</v>
       </c>
       <c r="W84">
-        <v>0.12543014554964</v>
+        <v>0.179687613675548</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8087289755661504</v>
+        <v>0.5841187008757197</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2015327516867925</v>
+        <v>0.2030827516867925</v>
       </c>
       <c r="C85">
-        <v>-93.45912948655378</v>
+        <v>-96.61424837685611</v>
       </c>
       <c r="D85">
-        <v>97.20387051344625</v>
+        <v>96.38975162314392</v>
       </c>
       <c r="E85">
-        <v>125.103</v>
+        <v>127.444</v>
       </c>
       <c r="F85">
-        <v>194.303</v>
+        <v>196.644</v>
       </c>
       <c r="G85">
         <v>3.64</v>
@@ -8257,37 +8257,37 @@
         <v>22.79</v>
       </c>
       <c r="M85">
-        <v>39.0160424</v>
+        <v>39.48611520000001</v>
       </c>
       <c r="N85">
-        <v>-16.2260424</v>
+        <v>-16.69611520000001</v>
       </c>
       <c r="O85">
-        <v>-2.920687632000001</v>
+        <v>-3.005300736000001</v>
       </c>
       <c r="P85">
-        <v>-13.305354768</v>
+        <v>-13.69081446400001</v>
       </c>
       <c r="Q85">
-        <v>-8.095354768000004</v>
+        <v>-8.480814464000005</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3081884255063983</v>
+        <v>0.3245877021005482</v>
       </c>
       <c r="T85">
-        <v>4.424245806919881</v>
+        <v>4.700761169852374</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1051413661576295</v>
+        <v>0.1038896832271816</v>
       </c>
       <c r="W85">
-        <v>0.179687613675548</v>
+        <v>0.1799389516079819</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5841187008757197</v>
+        <v>0.5771649068176754</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2030827516867925</v>
+        <v>0.2046327516867925</v>
       </c>
       <c r="C86">
-        <v>-96.61424837685608</v>
+        <v>-99.75584343196088</v>
       </c>
       <c r="D86">
-        <v>96.38975162314392</v>
+        <v>95.58915656803913</v>
       </c>
       <c r="E86">
-        <v>127.444</v>
+        <v>129.785</v>
       </c>
       <c r="F86">
-        <v>196.644</v>
+        <v>198.985</v>
       </c>
       <c r="G86">
         <v>3.64</v>
@@ -8339,37 +8339,37 @@
         <v>22.79</v>
       </c>
       <c r="M86">
-        <v>39.4861152</v>
+        <v>39.956188</v>
       </c>
       <c r="N86">
-        <v>-16.6961152</v>
+        <v>-17.16618800000001</v>
       </c>
       <c r="O86">
-        <v>-3.005300736</v>
+        <v>-3.089913840000001</v>
       </c>
       <c r="P86">
-        <v>-13.690814464</v>
+        <v>-14.07627416</v>
       </c>
       <c r="Q86">
-        <v>-8.480814464000002</v>
+        <v>-8.866274160000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.324587702100548</v>
+        <v>0.3431735489072513</v>
       </c>
       <c r="T86">
-        <v>4.70076116985237</v>
+        <v>5.01414524784253</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1038896832271816</v>
+        <v>0.102667451659803</v>
       </c>
       <c r="W86">
-        <v>0.1799389516079819</v>
+        <v>0.1801843757067116</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5771649068176754</v>
+        <v>0.5703747314433498</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2046327516867925</v>
+        <v>0.2061827516867925</v>
       </c>
       <c r="C87">
-        <v>-99.75584343196088</v>
+        <v>-102.8842488552933</v>
       </c>
       <c r="D87">
-        <v>95.58915656803913</v>
+        <v>94.80175114470676</v>
       </c>
       <c r="E87">
-        <v>129.785</v>
+        <v>132.126</v>
       </c>
       <c r="F87">
-        <v>198.985</v>
+        <v>201.326</v>
       </c>
       <c r="G87">
         <v>3.64</v>
@@ -8421,37 +8421,37 @@
         <v>22.79</v>
       </c>
       <c r="M87">
-        <v>39.956188</v>
+        <v>40.42626080000001</v>
       </c>
       <c r="N87">
-        <v>-17.16618800000001</v>
+        <v>-17.63626080000001</v>
       </c>
       <c r="O87">
-        <v>-3.089913840000001</v>
+        <v>-3.174526944000001</v>
       </c>
       <c r="P87">
-        <v>-14.07627416</v>
+        <v>-14.46173385600001</v>
       </c>
       <c r="Q87">
-        <v>-8.866274160000003</v>
+        <v>-9.251733856000008</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3431735489072513</v>
+        <v>0.3644145166863406</v>
       </c>
       <c r="T87">
-        <v>5.01414524784253</v>
+        <v>5.372298479831282</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.102667451659803</v>
+        <v>0.1014736440823634</v>
       </c>
       <c r="W87">
-        <v>0.1801843757067116</v>
+        <v>0.1804240922682614</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5703747314433498</v>
+        <v>0.563742467124241</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2061827516867925</v>
+        <v>0.2077327516867925</v>
       </c>
       <c r="C88">
-        <v>-102.8842488552933</v>
+        <v>-105.9997879283869</v>
       </c>
       <c r="D88">
-        <v>94.80175114470676</v>
+        <v>94.02721207161312</v>
       </c>
       <c r="E88">
-        <v>132.126</v>
+        <v>134.467</v>
       </c>
       <c r="F88">
-        <v>201.326</v>
+        <v>203.667</v>
       </c>
       <c r="G88">
         <v>3.64</v>
@@ -8503,37 +8503,37 @@
         <v>22.79</v>
       </c>
       <c r="M88">
-        <v>40.42626080000001</v>
+        <v>40.89633360000001</v>
       </c>
       <c r="N88">
-        <v>-17.63626080000001</v>
+        <v>-18.10633360000001</v>
       </c>
       <c r="O88">
-        <v>-3.174526944000001</v>
+        <v>-3.259140048000001</v>
       </c>
       <c r="P88">
-        <v>-14.46173385600001</v>
+        <v>-14.84719355200001</v>
       </c>
       <c r="Q88">
-        <v>-9.251733856000008</v>
+        <v>-9.637193552000006</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3644145166863406</v>
+        <v>0.3889233256622129</v>
       </c>
       <c r="T88">
-        <v>5.372298479831282</v>
+        <v>5.785552209049072</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1014736440823634</v>
+        <v>0.1003072803572787</v>
       </c>
       <c r="W88">
-        <v>0.1804240922682614</v>
+        <v>0.1806582981042584</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.563742467124241</v>
+        <v>0.5572626686515487</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2077327516867925</v>
+        <v>0.2092827516867925</v>
       </c>
       <c r="C89">
-        <v>-105.9997879283869</v>
+        <v>-109.1027734534325</v>
       </c>
       <c r="D89">
-        <v>94.02721207161312</v>
+        <v>93.26522654656748</v>
       </c>
       <c r="E89">
-        <v>134.467</v>
+        <v>136.808</v>
       </c>
       <c r="F89">
-        <v>203.667</v>
+        <v>206.008</v>
       </c>
       <c r="G89">
         <v>3.64</v>
@@ -8585,37 +8585,37 @@
         <v>22.79</v>
       </c>
       <c r="M89">
-        <v>40.89633360000001</v>
+        <v>41.3664064</v>
       </c>
       <c r="N89">
-        <v>-18.10633360000001</v>
+        <v>-18.5764064</v>
       </c>
       <c r="O89">
-        <v>-3.259140048000001</v>
+        <v>-3.343753152000001</v>
       </c>
       <c r="P89">
-        <v>-14.84719355200001</v>
+        <v>-15.232653248</v>
       </c>
       <c r="Q89">
-        <v>-9.637193552000006</v>
+        <v>-10.022653248</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3889233256622129</v>
+        <v>0.417516936134064</v>
       </c>
       <c r="T89">
-        <v>5.785552209049072</v>
+        <v>6.267681559803162</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1003072803572787</v>
+        <v>0.09916742489867332</v>
       </c>
       <c r="W89">
-        <v>0.1806582981042584</v>
+        <v>0.1808871810803464</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5572626686515487</v>
+        <v>0.5509301383259629</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2092827516867925</v>
+        <v>0.2108327516867925</v>
       </c>
       <c r="C90">
-        <v>-109.1027734534325</v>
+        <v>-112.1935081744815</v>
       </c>
       <c r="D90">
-        <v>93.26522654656748</v>
+        <v>92.51549182551848</v>
       </c>
       <c r="E90">
-        <v>136.808</v>
+        <v>139.149</v>
       </c>
       <c r="F90">
-        <v>206.008</v>
+        <v>208.349</v>
       </c>
       <c r="G90">
         <v>3.64</v>
@@ -8667,37 +8667,37 @@
         <v>22.79</v>
       </c>
       <c r="M90">
-        <v>41.3664064</v>
+        <v>41.83647920000001</v>
       </c>
       <c r="N90">
-        <v>-18.5764064</v>
+        <v>-19.04647920000001</v>
       </c>
       <c r="O90">
-        <v>-3.343753152000001</v>
+        <v>-3.428366256000001</v>
       </c>
       <c r="P90">
-        <v>-15.232653248</v>
+        <v>-15.61811294400001</v>
       </c>
       <c r="Q90">
-        <v>-10.022653248</v>
+        <v>-10.40811294400001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.417516936134064</v>
+        <v>0.4513093848735245</v>
       </c>
       <c r="T90">
-        <v>6.267681559803162</v>
+        <v>6.837470792512541</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.09916742489867332</v>
+        <v>0.09805318416947473</v>
       </c>
       <c r="W90">
-        <v>0.1808871810803464</v>
+        <v>0.1811109206187695</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5509301383259629</v>
+        <v>0.5447399120526375</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2108327516867925</v>
+        <v>0.2123827516867925</v>
       </c>
       <c r="C91">
-        <v>-112.1935081744815</v>
+        <v>-115.2722851784956</v>
       </c>
       <c r="D91">
-        <v>92.51549182551848</v>
+        <v>91.77771482150446</v>
       </c>
       <c r="E91">
-        <v>139.149</v>
+        <v>141.49</v>
       </c>
       <c r="F91">
-        <v>208.349</v>
+        <v>210.69</v>
       </c>
       <c r="G91">
         <v>3.64</v>
@@ -8749,37 +8749,37 @@
         <v>22.79</v>
       </c>
       <c r="M91">
-        <v>41.83647920000001</v>
+        <v>42.306552</v>
       </c>
       <c r="N91">
-        <v>-19.04647920000001</v>
+        <v>-19.516552</v>
       </c>
       <c r="O91">
-        <v>-3.428366256000001</v>
+        <v>-3.512979360000001</v>
       </c>
       <c r="P91">
-        <v>-15.61811294400001</v>
+        <v>-16.00357264000001</v>
       </c>
       <c r="Q91">
-        <v>-10.40811294400001</v>
+        <v>-10.79357264</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4513093848735245</v>
+        <v>0.4918603233608769</v>
       </c>
       <c r="T91">
-        <v>6.837470792512541</v>
+        <v>7.521217871763795</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.09805318416947473</v>
+        <v>0.09696370434536948</v>
       </c>
       <c r="W91">
-        <v>0.1811109206187695</v>
+        <v>0.1813296881674498</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5447399120526375</v>
+        <v>0.5386872463631638</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2123827516867925</v>
+        <v>0.2139327516867925</v>
       </c>
       <c r="C92">
-        <v>-115.2722851784956</v>
+        <v>-118.3393882773589</v>
       </c>
       <c r="D92">
-        <v>91.77771482150446</v>
+        <v>91.0516117226411</v>
       </c>
       <c r="E92">
-        <v>141.49</v>
+        <v>143.831</v>
       </c>
       <c r="F92">
-        <v>210.69</v>
+        <v>213.031</v>
       </c>
       <c r="G92">
         <v>3.64</v>
@@ -8831,37 +8831,37 @@
         <v>22.79</v>
       </c>
       <c r="M92">
-        <v>42.306552</v>
+        <v>42.77662480000001</v>
       </c>
       <c r="N92">
-        <v>-19.516552</v>
+        <v>-19.98662480000001</v>
       </c>
       <c r="O92">
-        <v>-3.512979360000001</v>
+        <v>-3.597592464000001</v>
       </c>
       <c r="P92">
-        <v>-16.00357264000001</v>
+        <v>-16.38903233600001</v>
       </c>
       <c r="Q92">
-        <v>-10.79357264</v>
+        <v>-11.17903233600001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4918603233608769</v>
+        <v>0.5414225815120856</v>
       </c>
       <c r="T92">
-        <v>7.521217871763795</v>
+        <v>8.356908746404219</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.09696370434536948</v>
+        <v>0.09589816913278298</v>
       </c>
       <c r="W92">
-        <v>0.1813296881674498</v>
+        <v>0.1815436476381372</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5386872463631638</v>
+        <v>0.5327676062932388</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2139327516867925</v>
+        <v>0.2154827516867925</v>
       </c>
       <c r="C93">
-        <v>-118.3393882773589</v>
+        <v>-121.3950923718994</v>
       </c>
       <c r="D93">
-        <v>91.0516117226411</v>
+        <v>90.33690762810065</v>
       </c>
       <c r="E93">
-        <v>143.831</v>
+        <v>146.172</v>
       </c>
       <c r="F93">
-        <v>213.031</v>
+        <v>215.372</v>
       </c>
       <c r="G93">
         <v>3.64</v>
@@ -8913,37 +8913,37 @@
         <v>22.79</v>
       </c>
       <c r="M93">
-        <v>42.77662480000001</v>
+        <v>43.24669760000001</v>
       </c>
       <c r="N93">
-        <v>-19.98662480000001</v>
+        <v>-20.45669760000001</v>
       </c>
       <c r="O93">
-        <v>-3.597592464000001</v>
+        <v>-3.682205568000002</v>
       </c>
       <c r="P93">
-        <v>-16.38903233600001</v>
+        <v>-16.77449203200001</v>
       </c>
       <c r="Q93">
-        <v>-11.17903233600001</v>
+        <v>-11.56449203200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5414225815120856</v>
+        <v>0.6033754042010964</v>
       </c>
       <c r="T93">
-        <v>8.356908746404219</v>
+        <v>9.401522339704748</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09589816913278298</v>
+        <v>0.09485579772916578</v>
       </c>
       <c r="W93">
-        <v>0.1815436476381372</v>
+        <v>0.1817529558159835</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5327676062932388</v>
+        <v>0.5269766540509209</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2154827516867925</v>
+        <v>0.2170327516867925</v>
       </c>
       <c r="C94">
-        <v>-121.3950923718994</v>
+        <v>-124.4396637988983</v>
       </c>
       <c r="D94">
-        <v>90.33690762810065</v>
+        <v>89.63333620110173</v>
       </c>
       <c r="E94">
-        <v>146.172</v>
+        <v>148.513</v>
       </c>
       <c r="F94">
-        <v>215.372</v>
+        <v>217.713</v>
       </c>
       <c r="G94">
         <v>3.64</v>
@@ -8995,37 +8995,37 @@
         <v>22.79</v>
       </c>
       <c r="M94">
-        <v>43.24669760000001</v>
+        <v>43.71677040000001</v>
       </c>
       <c r="N94">
-        <v>-20.45669760000001</v>
+        <v>-20.92677040000001</v>
       </c>
       <c r="O94">
-        <v>-3.682205568000002</v>
+        <v>-3.766818672000002</v>
       </c>
       <c r="P94">
-        <v>-16.77449203200001</v>
+        <v>-17.15995172800001</v>
       </c>
       <c r="Q94">
-        <v>-11.56449203200001</v>
+        <v>-11.94995172800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6033754042010964</v>
+        <v>0.6830290333726816</v>
       </c>
       <c r="T94">
-        <v>9.401522339704748</v>
+        <v>10.74459695966257</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09485579772916578</v>
+        <v>0.09383584291487367</v>
       </c>
       <c r="W94">
-        <v>0.1817529558159835</v>
+        <v>0.1819577627426934</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5269766540509209</v>
+        <v>0.5213102384159649</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2170327516867925</v>
+        <v>0.2185827516867925</v>
       </c>
       <c r="C95">
-        <v>-124.4396637988983</v>
+        <v>-127.4733606620103</v>
       </c>
       <c r="D95">
-        <v>89.63333620110173</v>
+        <v>88.94063933798972</v>
       </c>
       <c r="E95">
-        <v>148.513</v>
+        <v>150.854</v>
       </c>
       <c r="F95">
-        <v>217.713</v>
+        <v>220.054</v>
       </c>
       <c r="G95">
         <v>3.64</v>
@@ -9077,37 +9077,37 @@
         <v>22.79</v>
       </c>
       <c r="M95">
-        <v>43.71677040000001</v>
+        <v>44.18684320000001</v>
       </c>
       <c r="N95">
-        <v>-20.92677040000001</v>
+        <v>-21.39684320000001</v>
       </c>
       <c r="O95">
-        <v>-3.766818672000002</v>
+        <v>-3.851431776000001</v>
       </c>
       <c r="P95">
-        <v>-17.15995172800001</v>
+        <v>-17.545411424</v>
       </c>
       <c r="Q95">
-        <v>-11.94995172800001</v>
+        <v>-12.335411424</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6830290333726816</v>
+        <v>0.7892338722681288</v>
       </c>
       <c r="T95">
-        <v>10.74459695966257</v>
+        <v>12.53536311960634</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09383584291487367</v>
+        <v>0.0928375892668431</v>
       </c>
       <c r="W95">
-        <v>0.1819577627426934</v>
+        <v>0.1821582120752179</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5213102384159649</v>
+        <v>0.5157643848157951</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2185827516867925</v>
+        <v>0.2201327516867925</v>
       </c>
       <c r="C96">
-        <v>-127.4733606620103</v>
+        <v>-130.4964331474565</v>
       </c>
       <c r="D96">
-        <v>88.94063933798972</v>
+        <v>88.25856685254352</v>
       </c>
       <c r="E96">
-        <v>150.854</v>
+        <v>153.1950000000001</v>
       </c>
       <c r="F96">
-        <v>220.054</v>
+        <v>222.395</v>
       </c>
       <c r="G96">
         <v>3.64</v>
@@ -9159,37 +9159,37 @@
         <v>22.79</v>
       </c>
       <c r="M96">
-        <v>44.18684320000001</v>
+        <v>44.65691600000001</v>
       </c>
       <c r="N96">
-        <v>-21.39684320000001</v>
+        <v>-21.86691600000001</v>
       </c>
       <c r="O96">
-        <v>-3.851431776000001</v>
+        <v>-3.936044880000002</v>
       </c>
       <c r="P96">
-        <v>-17.545411424</v>
+        <v>-17.93087112000001</v>
       </c>
       <c r="Q96">
-        <v>-12.335411424</v>
+        <v>-12.72087112000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7892338722681288</v>
+        <v>0.9379206467217549</v>
       </c>
       <c r="T96">
-        <v>12.53536311960634</v>
+        <v>15.04243574352761</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.0928375892668431</v>
+        <v>0.09186035148508685</v>
       </c>
       <c r="W96">
-        <v>0.1821582120752179</v>
+        <v>0.1823544414217945</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5157643848157951</v>
+        <v>0.5103352860282603</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2201327516867925</v>
+        <v>0.2216827516867925</v>
       </c>
       <c r="C97">
-        <v>-130.4964331474565</v>
+        <v>-133.509123825302</v>
       </c>
       <c r="D97">
-        <v>88.25856685254352</v>
+        <v>87.58687617469805</v>
       </c>
       <c r="E97">
-        <v>153.1950000000001</v>
+        <v>155.5360000000001</v>
       </c>
       <c r="F97">
-        <v>222.395</v>
+        <v>224.736</v>
       </c>
       <c r="G97">
         <v>3.64</v>
@@ -9241,37 +9241,37 @@
         <v>22.79</v>
       </c>
       <c r="M97">
-        <v>44.65691600000001</v>
+        <v>45.12698880000001</v>
       </c>
       <c r="N97">
-        <v>-21.86691600000001</v>
+        <v>-22.33698880000001</v>
       </c>
       <c r="O97">
-        <v>-3.936044880000002</v>
+        <v>-4.020657984000002</v>
       </c>
       <c r="P97">
-        <v>-17.93087112000001</v>
+        <v>-18.31633081600001</v>
       </c>
       <c r="Q97">
-        <v>-12.72087112000001</v>
+        <v>-13.10633081600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9379206467217549</v>
+        <v>1.160950808402194</v>
       </c>
       <c r="T97">
-        <v>15.04243574352761</v>
+        <v>18.80304467940952</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09186035148508685</v>
+        <v>0.09090347282378386</v>
       </c>
       <c r="W97">
-        <v>0.1823544414217945</v>
+        <v>0.1825465826569842</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5103352860282603</v>
+        <v>0.5050192934654658</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2216827516867925</v>
+        <v>0.2578157841070977</v>
       </c>
       <c r="C98">
-        <v>-133.509123825302</v>
+        <v>-149.0477376065371</v>
       </c>
       <c r="D98">
-        <v>87.58687617469805</v>
+        <v>74.38926239346293</v>
       </c>
       <c r="E98">
-        <v>155.536</v>
+        <v>157.877</v>
       </c>
       <c r="F98">
-        <v>224.736</v>
+        <v>227.077</v>
       </c>
       <c r="G98">
         <v>3.64</v>
@@ -9323,45 +9323,45 @@
         <v>22.79</v>
       </c>
       <c r="M98">
-        <v>45.12698880000001</v>
+        <v>53.54475660000001</v>
       </c>
       <c r="N98">
-        <v>-22.33698880000001</v>
+        <v>-30.75475660000001</v>
       </c>
       <c r="O98">
-        <v>-4.020657984000001</v>
+        <v>-5.535856188000001</v>
       </c>
       <c r="P98">
-        <v>-18.316330816</v>
+        <v>-25.21890041200001</v>
       </c>
       <c r="Q98">
-        <v>-13.106330816</v>
+        <v>-20.00890041200001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.160950808402191</v>
+        <v>1.553768825213094</v>
       </c>
       <c r="T98">
-        <v>18.80304467940947</v>
+        <v>25.4265207736926</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09090347282378386</v>
+        <v>0.07661254360805142</v>
       </c>
       <c r="W98">
-        <v>0.1825465826569842</v>
+        <v>0.2177347622172215</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.505019293465466</v>
+        <v>0.4256252422669523</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2578157841070977</v>
+        <v>0.2597157841070977</v>
       </c>
       <c r="C99">
-        <v>-149.0477376065371</v>
+        <v>-151.9735119898818</v>
       </c>
       <c r="D99">
-        <v>74.38926239346293</v>
+        <v>73.80448801011823</v>
       </c>
       <c r="E99">
-        <v>157.877</v>
+        <v>160.218</v>
       </c>
       <c r="F99">
-        <v>227.077</v>
+        <v>229.418</v>
       </c>
       <c r="G99">
         <v>3.64</v>
@@ -9405,37 +9405,37 @@
         <v>22.79</v>
       </c>
       <c r="M99">
-        <v>53.54475660000001</v>
+        <v>54.0967644</v>
       </c>
       <c r="N99">
-        <v>-30.75475660000001</v>
+        <v>-31.30676440000001</v>
       </c>
       <c r="O99">
-        <v>-5.535856188000001</v>
+        <v>-5.635217592000001</v>
       </c>
       <c r="P99">
-        <v>-25.21890041200001</v>
+        <v>-25.67154680800001</v>
       </c>
       <c r="Q99">
-        <v>-20.00890041200001</v>
+        <v>-20.461546808</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.553768825213094</v>
+        <v>2.30775323781964</v>
       </c>
       <c r="T99">
-        <v>25.4265207736926</v>
+        <v>38.1397811605389</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07661254360805142</v>
+        <v>0.07583078295898968</v>
       </c>
       <c r="W99">
-        <v>0.2177347622172215</v>
+        <v>0.2179191013782702</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4256252422669523</v>
+        <v>0.4212821275499427</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2597157841070977</v>
+        <v>0.2616157841070977</v>
       </c>
       <c r="C100">
-        <v>-151.9735119898818</v>
+        <v>-154.8901642532469</v>
       </c>
       <c r="D100">
-        <v>73.80448801011823</v>
+        <v>73.22883574675311</v>
       </c>
       <c r="E100">
-        <v>160.218</v>
+        <v>162.559</v>
       </c>
       <c r="F100">
-        <v>229.418</v>
+        <v>231.759</v>
       </c>
       <c r="G100">
         <v>3.64</v>
@@ -9487,37 +9487,37 @@
         <v>22.79</v>
       </c>
       <c r="M100">
-        <v>54.0967644</v>
+        <v>54.6487722</v>
       </c>
       <c r="N100">
-        <v>-31.30676440000001</v>
+        <v>-31.8587722</v>
       </c>
       <c r="O100">
-        <v>-5.635217592000001</v>
+        <v>-5.734578996000001</v>
       </c>
       <c r="P100">
-        <v>-25.67154680800001</v>
+        <v>-26.124193204</v>
       </c>
       <c r="Q100">
-        <v>-20.461546808</v>
+        <v>-20.914193204</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.30775323781964</v>
+        <v>4.569706475639281</v>
       </c>
       <c r="T100">
-        <v>38.1397811605389</v>
+        <v>76.27956232107779</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07583078295898968</v>
+        <v>0.07506481545435342</v>
       </c>
       <c r="W100">
-        <v>0.2179191013782702</v>
+        <v>0.2180997165158635</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4212821275499427</v>
+        <v>0.4170267525241856</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2616157841070977</v>
-      </c>
-      <c r="C101">
-        <v>-154.8901642532469</v>
-      </c>
-      <c r="D101">
-        <v>73.22883574675311</v>
-      </c>
-      <c r="E101">
-        <v>162.559</v>
-      </c>
-      <c r="F101">
-        <v>231.759</v>
-      </c>
-      <c r="G101">
-        <v>3.64</v>
-      </c>
-      <c r="H101">
-        <v>164.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>28</v>
-      </c>
-      <c r="K101">
-        <v>5.21</v>
-      </c>
-      <c r="L101">
-        <v>22.79</v>
-      </c>
-      <c r="M101">
-        <v>54.6487722</v>
-      </c>
-      <c r="N101">
-        <v>-31.8587722</v>
-      </c>
-      <c r="O101">
-        <v>-5.734578996000001</v>
-      </c>
-      <c r="P101">
-        <v>-26.124193204</v>
-      </c>
-      <c r="Q101">
-        <v>-20.914193204</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.569706475639281</v>
-      </c>
-      <c r="T101">
-        <v>76.27956232107779</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07506481545435342</v>
-      </c>
-      <c r="W101">
-        <v>0.2180997165158635</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4170267525241856</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
